--- a/research/traditional_assets/database/data/malaysia/malaysia_chemical_diversified.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_chemical_diversified.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09623505296297355</v>
+        <v>0.09603828883586242</v>
       </c>
       <c r="C2">
-        <v>330.1811490741516</v>
+        <v>327.9364431334338</v>
       </c>
       <c r="D2">
-        <v>309.7811490741516</v>
+        <v>310.9944431334338</v>
       </c>
       <c r="E2">
-        <v>-88</v>
+        <v>-84.542</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.458</v>
       </c>
       <c r="G2">
         <v>20.4</v>
@@ -1582,28 +1582,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1739374</v>
       </c>
       <c r="N2">
-        <v>29.07959183673469</v>
+        <v>28.90565443673469</v>
       </c>
       <c r="O2">
-        <v>6.979102040816326</v>
+        <v>6.937357064816326</v>
       </c>
       <c r="P2">
-        <v>22.10048979591837</v>
+        <v>21.96829737191837</v>
       </c>
       <c r="Q2">
-        <v>27.00048979591837</v>
+        <v>26.86829737191837</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09623505296297355</v>
+        <v>0.09662223114733579</v>
       </c>
       <c r="T2">
-        <v>0.8504074490426663</v>
+        <v>0.8569358294595595</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>167.1842389085654</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09603828883586242</v>
+        <v>0.09584152470875129</v>
       </c>
       <c r="C3">
-        <v>327.9364431334338</v>
+        <v>325.7012785785109</v>
       </c>
       <c r="D3">
-        <v>310.9944431334338</v>
+        <v>312.2172785785109</v>
       </c>
       <c r="E3">
-        <v>-84.542</v>
+        <v>-81.084</v>
       </c>
       <c r="F3">
-        <v>3.458</v>
+        <v>6.916</v>
       </c>
       <c r="G3">
         <v>20.4</v>
@@ -1664,28 +1664,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M3">
-        <v>0.1739374</v>
+        <v>0.3478748</v>
       </c>
       <c r="N3">
-        <v>28.90565443673469</v>
+        <v>28.73171703673469</v>
       </c>
       <c r="O3">
-        <v>6.937357064816326</v>
+        <v>6.895612088816326</v>
       </c>
       <c r="P3">
-        <v>21.96829737191837</v>
+        <v>21.83610494791837</v>
       </c>
       <c r="Q3">
-        <v>26.86829737191837</v>
+        <v>26.73610494791837</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09662223114733579</v>
+        <v>0.09701731092729723</v>
       </c>
       <c r="T3">
-        <v>0.8569358294595595</v>
+        <v>0.8635974421298587</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>167.1842389085654</v>
+        <v>83.59211945428268</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09584152470875129</v>
+        <v>0.09564476058164015</v>
       </c>
       <c r="C4">
-        <v>325.7012785785109</v>
+        <v>323.4757684043552</v>
       </c>
       <c r="D4">
-        <v>312.2172785785109</v>
+        <v>313.4497684043552</v>
       </c>
       <c r="E4">
-        <v>-81.084</v>
+        <v>-77.626</v>
       </c>
       <c r="F4">
-        <v>6.916</v>
+        <v>10.374</v>
       </c>
       <c r="G4">
         <v>20.4</v>
@@ -1746,28 +1746,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M4">
-        <v>0.3478748</v>
+        <v>0.5218121999999999</v>
       </c>
       <c r="N4">
-        <v>28.73171703673469</v>
+        <v>28.55777963673469</v>
       </c>
       <c r="O4">
-        <v>6.895612088816326</v>
+        <v>6.853867112816326</v>
       </c>
       <c r="P4">
-        <v>21.83610494791837</v>
+        <v>21.70391252391837</v>
       </c>
       <c r="Q4">
-        <v>26.73610494791837</v>
+        <v>26.60391252391837</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09701731092729723</v>
+        <v>0.09742053668210325</v>
       </c>
       <c r="T4">
-        <v>0.8635974421298587</v>
+        <v>0.8703964076387208</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>83.59211945428268</v>
+        <v>55.72807963618845</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09564476058164015</v>
+        <v>0.095447996454529</v>
       </c>
       <c r="C5">
-        <v>323.4757684043552</v>
+        <v>321.2600273972183</v>
       </c>
       <c r="D5">
-        <v>313.4497684043552</v>
+        <v>314.6920273972183</v>
       </c>
       <c r="E5">
-        <v>-77.626</v>
+        <v>-74.16800000000001</v>
       </c>
       <c r="F5">
-        <v>10.374</v>
+        <v>13.832</v>
       </c>
       <c r="G5">
         <v>20.4</v>
@@ -1828,28 +1828,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M5">
-        <v>0.5218121999999999</v>
+        <v>0.6957496</v>
       </c>
       <c r="N5">
-        <v>28.55777963673469</v>
+        <v>28.38384223673469</v>
       </c>
       <c r="O5">
-        <v>6.853867112816326</v>
+        <v>6.812122136816326</v>
       </c>
       <c r="P5">
-        <v>21.70391252391837</v>
+        <v>21.57172009991837</v>
       </c>
       <c r="Q5">
-        <v>26.60391252391837</v>
+        <v>26.47172009991836</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09742053668210325</v>
+        <v>0.09783216297346772</v>
       </c>
       <c r="T5">
-        <v>0.8703964076387208</v>
+        <v>0.8773370182623508</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.72807963618845</v>
+        <v>41.79605972714134</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.095447996454529</v>
+        <v>0.09525123232741786</v>
       </c>
       <c r="C6">
-        <v>321.2600273972183</v>
+        <v>319.0541721702681</v>
       </c>
       <c r="D6">
-        <v>314.6920273972183</v>
+        <v>315.9441721702681</v>
       </c>
       <c r="E6">
-        <v>-74.16800000000001</v>
+        <v>-70.70999999999999</v>
       </c>
       <c r="F6">
-        <v>13.832</v>
+        <v>17.29</v>
       </c>
       <c r="G6">
         <v>20.4</v>
@@ -1910,28 +1910,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M6">
-        <v>0.6957496</v>
+        <v>0.8696870000000001</v>
       </c>
       <c r="N6">
-        <v>28.38384223673469</v>
+        <v>28.20990483673469</v>
       </c>
       <c r="O6">
-        <v>6.812122136816326</v>
+        <v>6.770377160816326</v>
       </c>
       <c r="P6">
-        <v>21.57172009991837</v>
+        <v>21.43952767591837</v>
       </c>
       <c r="Q6">
-        <v>26.47172009991836</v>
+        <v>26.33952767591837</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09783216297346772</v>
+        <v>0.0982524550814925</v>
       </c>
       <c r="T6">
-        <v>0.8773370182623508</v>
+        <v>0.884423747004373</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.79605972714134</v>
+        <v>33.43684778171306</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09525123232741786</v>
+        <v>0.09505446820030675</v>
       </c>
       <c r="C7">
-        <v>319.0541721702681</v>
+        <v>316.8583212000802</v>
       </c>
       <c r="D7">
-        <v>315.9441721702681</v>
+        <v>317.2063212000802</v>
       </c>
       <c r="E7">
-        <v>-70.70999999999999</v>
+        <v>-67.252</v>
       </c>
       <c r="F7">
-        <v>17.29</v>
+        <v>20.748</v>
       </c>
       <c r="G7">
         <v>20.4</v>
@@ -1992,28 +1992,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M7">
-        <v>0.8696870000000001</v>
+        <v>1.0436244</v>
       </c>
       <c r="N7">
-        <v>28.20990483673469</v>
+        <v>28.03596743673469</v>
       </c>
       <c r="O7">
-        <v>6.770377160816326</v>
+        <v>6.728632184816326</v>
       </c>
       <c r="P7">
-        <v>21.43952767591837</v>
+        <v>21.30733525191837</v>
       </c>
       <c r="Q7">
-        <v>26.33952767591837</v>
+        <v>26.20733525191837</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0982524550814925</v>
+        <v>0.09868168957479441</v>
       </c>
       <c r="T7">
-        <v>0.884423747004373</v>
+        <v>0.8916612572089915</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.43684778171306</v>
+        <v>27.86403981809423</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09505446820030675</v>
+        <v>0.09485770407319562</v>
       </c>
       <c r="C8">
-        <v>316.8583212000802</v>
+        <v>314.6725948640075</v>
       </c>
       <c r="D8">
-        <v>317.2063212000802</v>
+        <v>318.4785948640076</v>
       </c>
       <c r="E8">
-        <v>-67.252</v>
+        <v>-63.794</v>
       </c>
       <c r="F8">
-        <v>20.748</v>
+        <v>24.206</v>
       </c>
       <c r="G8">
         <v>20.4</v>
@@ -2074,28 +2074,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M8">
-        <v>1.0436244</v>
+        <v>1.2175618</v>
       </c>
       <c r="N8">
-        <v>28.03596743673469</v>
+        <v>27.86203003673469</v>
       </c>
       <c r="O8">
-        <v>6.728632184816326</v>
+        <v>6.686887208816326</v>
       </c>
       <c r="P8">
-        <v>21.30733525191837</v>
+        <v>21.17514282791837</v>
       </c>
       <c r="Q8">
-        <v>26.20733525191837</v>
+        <v>26.07514282791837</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09868168957479441</v>
+        <v>0.09912015491741463</v>
       </c>
       <c r="T8">
-        <v>0.8916612572089915</v>
+        <v>0.8990544127943543</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.86403981809423</v>
+        <v>23.88346270122362</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0948577040731956</v>
+        <v>0.09466093994608447</v>
       </c>
       <c r="C9">
-        <v>314.6725948640076</v>
+        <v>312.4971154784523</v>
       </c>
       <c r="D9">
-        <v>318.4785948640076</v>
+        <v>319.7611154784523</v>
       </c>
       <c r="E9">
-        <v>-63.794</v>
+        <v>-60.336</v>
       </c>
       <c r="F9">
-        <v>24.206</v>
+        <v>27.664</v>
       </c>
       <c r="G9">
         <v>20.4</v>
@@ -2156,28 +2156,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M9">
-        <v>1.2175618</v>
+        <v>1.3914992</v>
       </c>
       <c r="N9">
-        <v>27.86203003673469</v>
+        <v>27.68809263673469</v>
       </c>
       <c r="O9">
-        <v>6.686887208816326</v>
+        <v>6.645142232816326</v>
       </c>
       <c r="P9">
-        <v>21.17514282791837</v>
+        <v>21.04295040391837</v>
       </c>
       <c r="Q9">
-        <v>26.07514282791837</v>
+        <v>25.94295040391837</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09912015491741463</v>
+        <v>0.0995681521153092</v>
       </c>
       <c r="T9">
-        <v>0.8990544127943543</v>
+        <v>0.9066082891533119</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.88346270122362</v>
+        <v>20.89802986357067</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09466093994608447</v>
+        <v>0.09446417581897333</v>
       </c>
       <c r="C10">
-        <v>312.4971154784523</v>
+        <v>310.3320073380668</v>
       </c>
       <c r="D10">
-        <v>319.7611154784523</v>
+        <v>321.0540073380669</v>
       </c>
       <c r="E10">
-        <v>-60.336</v>
+        <v>-56.878</v>
       </c>
       <c r="F10">
-        <v>27.664</v>
+        <v>31.122</v>
       </c>
       <c r="G10">
         <v>20.4</v>
@@ -2238,28 +2238,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M10">
-        <v>1.3914992</v>
+        <v>1.5654366</v>
       </c>
       <c r="N10">
-        <v>27.68809263673469</v>
+        <v>27.51415523673469</v>
       </c>
       <c r="O10">
-        <v>6.645142232816326</v>
+        <v>6.603397256816327</v>
       </c>
       <c r="P10">
-        <v>21.04295040391837</v>
+        <v>20.91075797991837</v>
       </c>
       <c r="Q10">
-        <v>25.94295040391837</v>
+        <v>25.81075797991837</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0995681521153092</v>
+        <v>0.1000259954054652</v>
       </c>
       <c r="T10">
-        <v>0.9066082891533119</v>
+        <v>0.9143281847729062</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.89802986357067</v>
+        <v>18.57602654539615</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09446417581897333</v>
+        <v>0.0942674116918622</v>
       </c>
       <c r="C11">
-        <v>310.3320073380668</v>
+        <v>308.1773967559097</v>
       </c>
       <c r="D11">
-        <v>321.0540073380669</v>
+        <v>322.3573967559097</v>
       </c>
       <c r="E11">
-        <v>-56.878</v>
+        <v>-53.42</v>
       </c>
       <c r="F11">
-        <v>31.122</v>
+        <v>34.58</v>
       </c>
       <c r="G11">
         <v>20.4</v>
@@ -2320,28 +2320,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M11">
-        <v>1.5654366</v>
+        <v>1.739374</v>
       </c>
       <c r="N11">
-        <v>27.51415523673469</v>
+        <v>27.34021783673469</v>
       </c>
       <c r="O11">
-        <v>6.603397256816327</v>
+        <v>6.561652280816326</v>
       </c>
       <c r="P11">
-        <v>20.91075797991837</v>
+        <v>20.77856555591837</v>
       </c>
       <c r="Q11">
-        <v>25.81075797991837</v>
+        <v>25.67856555591837</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1000259954054652</v>
+        <v>0.100494012990958</v>
       </c>
       <c r="T11">
-        <v>0.9143281847729062</v>
+        <v>0.9222196336284916</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.57602654539615</v>
+        <v>16.71842389085653</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0942674116918622</v>
+        <v>0.09407064756475106</v>
       </c>
       <c r="C12">
-        <v>308.1773967559097</v>
+        <v>306.0334121045832</v>
       </c>
       <c r="D12">
-        <v>322.3573967559097</v>
+        <v>323.6714121045833</v>
       </c>
       <c r="E12">
-        <v>-53.41999999999999</v>
+        <v>-49.962</v>
       </c>
       <c r="F12">
-        <v>34.58000000000001</v>
+        <v>38.038</v>
       </c>
       <c r="G12">
         <v>20.4</v>
@@ -2402,28 +2402,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M12">
-        <v>1.739374</v>
+        <v>1.9133114</v>
       </c>
       <c r="N12">
-        <v>27.34021783673469</v>
+        <v>27.16628043673469</v>
       </c>
       <c r="O12">
-        <v>6.561652280816325</v>
+        <v>6.519907304816326</v>
       </c>
       <c r="P12">
-        <v>20.77856555591837</v>
+        <v>20.64637313191837</v>
       </c>
       <c r="Q12">
-        <v>25.67856555591836</v>
+        <v>25.54637313191837</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.100494012990958</v>
+        <v>0.100972547825563</v>
       </c>
       <c r="T12">
-        <v>0.9222196336284916</v>
+        <v>0.9302884184134157</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.71842389085653</v>
+        <v>15.19856717350594</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09407064756475106</v>
+        <v>0.09387388343763992</v>
       </c>
       <c r="C13">
-        <v>306.0334121045832</v>
+        <v>303.9001838583818</v>
       </c>
       <c r="D13">
-        <v>323.6714121045833</v>
+        <v>324.9961838583818</v>
       </c>
       <c r="E13">
-        <v>-49.962</v>
+        <v>-46.504</v>
       </c>
       <c r="F13">
-        <v>38.038</v>
+        <v>41.496</v>
       </c>
       <c r="G13">
         <v>20.4</v>
@@ -2484,28 +2484,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M13">
-        <v>1.9133114</v>
+        <v>2.0872488</v>
       </c>
       <c r="N13">
-        <v>27.16628043673469</v>
+        <v>26.99234303673469</v>
       </c>
       <c r="O13">
-        <v>6.519907304816326</v>
+        <v>6.478162328816325</v>
       </c>
       <c r="P13">
-        <v>20.64637313191837</v>
+        <v>20.51418070791837</v>
       </c>
       <c r="Q13">
-        <v>25.54637313191837</v>
+        <v>25.41418070791837</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.100972547825563</v>
+        <v>0.1014619584518635</v>
       </c>
       <c r="T13">
-        <v>0.9302884184134157</v>
+        <v>0.9385405846707243</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.19856717350594</v>
+        <v>13.93201990904711</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09387388343763992</v>
+        <v>0.09382531931052877</v>
       </c>
       <c r="C14">
-        <v>303.9001838583818</v>
+        <v>300.7708262538957</v>
       </c>
       <c r="D14">
-        <v>324.9961838583818</v>
+        <v>325.3248262538958</v>
       </c>
       <c r="E14">
-        <v>-46.504</v>
+        <v>-43.046</v>
       </c>
       <c r="F14">
-        <v>41.496</v>
+        <v>44.954</v>
       </c>
       <c r="G14">
         <v>20.4</v>
@@ -2566,45 +2566,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M14">
-        <v>2.0872488</v>
+        <v>2.3286172</v>
       </c>
       <c r="N14">
-        <v>26.99234303673469</v>
+        <v>26.75097463673469</v>
       </c>
       <c r="O14">
-        <v>6.478162328816325</v>
+        <v>6.420233912816326</v>
       </c>
       <c r="P14">
-        <v>20.51418070791837</v>
+        <v>20.33074072391837</v>
       </c>
       <c r="Q14">
-        <v>25.41418070791837</v>
+        <v>25.23074072391837</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1014619584518635</v>
+        <v>0.1019626198971595</v>
       </c>
       <c r="T14">
-        <v>0.9385405846707243</v>
+        <v>0.9469824558994657</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.93201990904711</v>
+        <v>12.48792280531755</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09382531931052877</v>
+        <v>0.09363995518341765</v>
       </c>
       <c r="C15">
-        <v>300.7708262538957</v>
+        <v>298.5733531965931</v>
       </c>
       <c r="D15">
-        <v>325.3248262538958</v>
+        <v>326.5853531965931</v>
       </c>
       <c r="E15">
-        <v>-43.046</v>
+        <v>-39.58799999999999</v>
       </c>
       <c r="F15">
-        <v>44.954</v>
+        <v>48.41200000000001</v>
       </c>
       <c r="G15">
         <v>20.4</v>
@@ -2648,28 +2648,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M15">
-        <v>2.3286172</v>
+        <v>2.5077416</v>
       </c>
       <c r="N15">
-        <v>26.75097463673469</v>
+        <v>26.57185023673469</v>
       </c>
       <c r="O15">
-        <v>6.420233912816326</v>
+        <v>6.377244056816326</v>
       </c>
       <c r="P15">
-        <v>20.33074072391837</v>
+        <v>20.19460617991837</v>
       </c>
       <c r="Q15">
-        <v>25.23074072391837</v>
+        <v>25.09460617991837</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1019626198971595</v>
+        <v>0.102474924631881</v>
       </c>
       <c r="T15">
-        <v>0.9469824558994657</v>
+        <v>0.9556206497149218</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.48792280531755</v>
+        <v>11.59592831922344</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09363995518341765</v>
+        <v>0.0934545910563065</v>
       </c>
       <c r="C16">
-        <v>298.5733531965931</v>
+        <v>296.3856863917944</v>
       </c>
       <c r="D16">
-        <v>326.5853531965931</v>
+        <v>327.8556863917944</v>
       </c>
       <c r="E16">
-        <v>-39.58799999999999</v>
+        <v>-36.12999999999999</v>
       </c>
       <c r="F16">
-        <v>48.41200000000001</v>
+        <v>51.87000000000001</v>
       </c>
       <c r="G16">
         <v>20.4</v>
@@ -2730,28 +2730,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M16">
-        <v>2.5077416</v>
+        <v>2.686866000000001</v>
       </c>
       <c r="N16">
-        <v>26.57185023673469</v>
+        <v>26.39272583673469</v>
       </c>
       <c r="O16">
-        <v>6.377244056816326</v>
+        <v>6.334254200816326</v>
       </c>
       <c r="P16">
-        <v>20.19460617991837</v>
+        <v>20.05847163591837</v>
       </c>
       <c r="Q16">
-        <v>25.09460617991837</v>
+        <v>24.95847163591836</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.102474924631881</v>
+        <v>0.1029992835956547</v>
       </c>
       <c r="T16">
-        <v>0.9556206497149218</v>
+        <v>0.9644620951495652</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.59592831922344</v>
+        <v>10.82286643127521</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0934545910563065</v>
+        <v>0.09326922692919537</v>
       </c>
       <c r="C17">
-        <v>296.3856863917944</v>
+        <v>294.207940717762</v>
       </c>
       <c r="D17">
-        <v>327.8556863917944</v>
+        <v>329.135940717762</v>
       </c>
       <c r="E17">
-        <v>-36.13</v>
+        <v>-32.672</v>
       </c>
       <c r="F17">
-        <v>51.87</v>
+        <v>55.328</v>
       </c>
       <c r="G17">
         <v>20.4</v>
@@ -2812,28 +2812,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M17">
-        <v>2.686866</v>
+        <v>2.8659904</v>
       </c>
       <c r="N17">
-        <v>26.39272583673469</v>
+        <v>26.21360143673469</v>
       </c>
       <c r="O17">
-        <v>6.334254200816327</v>
+        <v>6.291264344816326</v>
       </c>
       <c r="P17">
-        <v>20.05847163591837</v>
+        <v>19.92233709191837</v>
       </c>
       <c r="Q17">
-        <v>24.95847163591836</v>
+        <v>24.82233709191836</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1029992835956547</v>
+        <v>0.1035361272966612</v>
       </c>
       <c r="T17">
-        <v>0.964462095149565</v>
+        <v>0.9735140511897952</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.82286643127521</v>
+        <v>10.14643727932051</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09326922692919537</v>
+        <v>0.09330350280208424</v>
       </c>
       <c r="C18">
-        <v>294.207940717762</v>
+        <v>290.5124546167011</v>
       </c>
       <c r="D18">
-        <v>329.135940717762</v>
+        <v>328.8984546167011</v>
       </c>
       <c r="E18">
-        <v>-32.672</v>
+        <v>-29.21399999999999</v>
       </c>
       <c r="F18">
-        <v>55.328</v>
+        <v>58.78600000000001</v>
       </c>
       <c r="G18">
         <v>20.4</v>
@@ -2894,45 +2894,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M18">
-        <v>2.8659904</v>
+        <v>3.145051</v>
       </c>
       <c r="N18">
-        <v>26.21360143673469</v>
+        <v>25.93454083673469</v>
       </c>
       <c r="O18">
-        <v>6.291264344816326</v>
+        <v>6.224289800816326</v>
       </c>
       <c r="P18">
-        <v>19.92233709191837</v>
+        <v>19.71025103591836</v>
       </c>
       <c r="Q18">
-        <v>24.82233709191836</v>
+        <v>24.61025103591836</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1035361272966612</v>
+        <v>0.1040859069904629</v>
       </c>
       <c r="T18">
-        <v>0.9735140511897952</v>
+        <v>0.9827841266526813</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.14643727932051</v>
+        <v>9.246143174382446</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09330350280208424</v>
+        <v>0.09313105867497309</v>
       </c>
       <c r="C19">
-        <v>290.5124546167011</v>
+        <v>288.2527503764486</v>
       </c>
       <c r="D19">
-        <v>328.8984546167011</v>
+        <v>330.0967503764487</v>
       </c>
       <c r="E19">
-        <v>-29.21399999999999</v>
+        <v>-25.75599999999999</v>
       </c>
       <c r="F19">
-        <v>58.78600000000001</v>
+        <v>62.24400000000001</v>
       </c>
       <c r="G19">
         <v>20.4</v>
@@ -2976,28 +2976,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M19">
-        <v>3.145051</v>
+        <v>3.330054000000001</v>
       </c>
       <c r="N19">
-        <v>25.93454083673469</v>
+        <v>25.74953783673469</v>
       </c>
       <c r="O19">
-        <v>6.224289800816326</v>
+        <v>6.179889080816326</v>
       </c>
       <c r="P19">
-        <v>19.71025103591836</v>
+        <v>19.56964875591837</v>
       </c>
       <c r="Q19">
-        <v>24.61025103591836</v>
+        <v>24.46964875591836</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1040859069904629</v>
+        <v>0.1046490959450891</v>
       </c>
       <c r="T19">
-        <v>0.9827841266526813</v>
+        <v>0.9922803015171014</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.246143174382446</v>
+        <v>8.732468553583422</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09313105867497311</v>
+        <v>0.09295861454786197</v>
       </c>
       <c r="C20">
-        <v>288.2527503764486</v>
+        <v>286.0018097128316</v>
       </c>
       <c r="D20">
-        <v>330.0967503764486</v>
+        <v>331.3038097128317</v>
       </c>
       <c r="E20">
-        <v>-25.756</v>
+        <v>-22.298</v>
       </c>
       <c r="F20">
-        <v>62.244</v>
+        <v>65.702</v>
       </c>
       <c r="G20">
         <v>20.4</v>
@@ -3058,28 +3058,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M20">
-        <v>3.330054</v>
+        <v>3.515057</v>
       </c>
       <c r="N20">
-        <v>25.74953783673469</v>
+        <v>25.56453483673469</v>
       </c>
       <c r="O20">
-        <v>6.179889080816326</v>
+        <v>6.135488360816327</v>
       </c>
       <c r="P20">
-        <v>19.56964875591837</v>
+        <v>19.42904647591837</v>
       </c>
       <c r="Q20">
-        <v>24.46964875591836</v>
+        <v>24.32904647591837</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1046490959450891</v>
+        <v>0.1052261907998296</v>
       </c>
       <c r="T20">
-        <v>0.9922803015171013</v>
+        <v>1.002010949834964</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.732468553583423</v>
+        <v>8.272864945500086</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09295861454786197</v>
+        <v>0.09278617042075084</v>
       </c>
       <c r="C21">
-        <v>286.0018097128316</v>
+        <v>283.7597291155606</v>
       </c>
       <c r="D21">
-        <v>331.3038097128317</v>
+        <v>332.5197291155607</v>
       </c>
       <c r="E21">
-        <v>-22.298</v>
+        <v>-18.83999999999999</v>
       </c>
       <c r="F21">
-        <v>65.702</v>
+        <v>69.16000000000001</v>
       </c>
       <c r="G21">
         <v>20.4</v>
@@ -3140,28 +3140,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M21">
-        <v>3.515057</v>
+        <v>3.700060000000001</v>
       </c>
       <c r="N21">
-        <v>25.56453483673469</v>
+        <v>25.37953183673469</v>
       </c>
       <c r="O21">
-        <v>6.135488360816327</v>
+        <v>6.091087640816326</v>
       </c>
       <c r="P21">
-        <v>19.42904647591837</v>
+        <v>19.28844419591837</v>
       </c>
       <c r="Q21">
-        <v>24.32904647591837</v>
+        <v>24.18844419591836</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1052261907998296</v>
+        <v>0.1058177130259385</v>
       </c>
       <c r="T21">
-        <v>1.002010949834964</v>
+        <v>1.011984864360773</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.272864945500086</v>
+        <v>7.859221698225079</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09278617042075084</v>
+        <v>0.09274140629363968</v>
       </c>
       <c r="C22">
-        <v>283.7597291155606</v>
+        <v>280.6188256108805</v>
       </c>
       <c r="D22">
-        <v>332.5197291155607</v>
+        <v>332.8368256108805</v>
       </c>
       <c r="E22">
-        <v>-18.83999999999999</v>
+        <v>-15.38199999999999</v>
       </c>
       <c r="F22">
-        <v>69.16000000000001</v>
+        <v>72.61800000000001</v>
       </c>
       <c r="G22">
         <v>20.4</v>
@@ -3222,45 +3222,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M22">
-        <v>3.700060000000001</v>
+        <v>3.9431574</v>
       </c>
       <c r="N22">
-        <v>25.37953183673469</v>
+        <v>25.13643443673469</v>
       </c>
       <c r="O22">
-        <v>6.091087640816326</v>
+        <v>6.032744264816326</v>
       </c>
       <c r="P22">
-        <v>19.28844419591837</v>
+        <v>19.10369017191837</v>
       </c>
       <c r="Q22">
-        <v>24.18844419591836</v>
+        <v>24.00369017191836</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1058177130259385</v>
+        <v>0.1064242104982781</v>
       </c>
       <c r="T22">
-        <v>1.011984864360773</v>
+        <v>1.022211283051792</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.859221698225079</v>
+        <v>7.374697199948115</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09274140629363968</v>
+        <v>0.09257504216652855</v>
       </c>
       <c r="C23">
-        <v>280.6188256108805</v>
+        <v>278.3446216140152</v>
       </c>
       <c r="D23">
-        <v>332.8368256108805</v>
+        <v>334.0206216140152</v>
       </c>
       <c r="E23">
-        <v>-15.38200000000001</v>
+        <v>-11.92399999999999</v>
       </c>
       <c r="F23">
-        <v>72.61799999999999</v>
+        <v>76.07600000000001</v>
       </c>
       <c r="G23">
         <v>20.4</v>
@@ -3304,28 +3304,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M23">
-        <v>3.9431574</v>
+        <v>4.1309268</v>
       </c>
       <c r="N23">
-        <v>25.13643443673469</v>
+        <v>24.94866503673469</v>
       </c>
       <c r="O23">
-        <v>6.032744264816326</v>
+        <v>5.987679608816326</v>
       </c>
       <c r="P23">
-        <v>19.10369017191837</v>
+        <v>18.96098542791837</v>
       </c>
       <c r="Q23">
-        <v>24.00369017191836</v>
+        <v>23.86098542791837</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1064242104982781</v>
+        <v>0.1070462591878571</v>
       </c>
       <c r="T23">
-        <v>1.022211283051792</v>
+        <v>1.032699917606684</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.374697199948116</v>
+        <v>7.039483690859565</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09257504216652855</v>
+        <v>0.09240867803941742</v>
       </c>
       <c r="C24">
-        <v>278.3446216140152</v>
+        <v>276.0788684549348</v>
       </c>
       <c r="D24">
-        <v>334.0206216140152</v>
+        <v>335.2128684549348</v>
       </c>
       <c r="E24">
-        <v>-11.92399999999999</v>
+        <v>-8.465999999999994</v>
       </c>
       <c r="F24">
-        <v>76.07600000000001</v>
+        <v>79.53400000000001</v>
       </c>
       <c r="G24">
         <v>20.4</v>
@@ -3386,28 +3386,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M24">
-        <v>4.1309268</v>
+        <v>4.318696200000001</v>
       </c>
       <c r="N24">
-        <v>24.94866503673469</v>
+        <v>24.76089563673469</v>
       </c>
       <c r="O24">
-        <v>5.987679608816326</v>
+        <v>5.942614952816326</v>
       </c>
       <c r="P24">
-        <v>18.96098542791837</v>
+        <v>18.81828068391837</v>
       </c>
       <c r="Q24">
-        <v>23.86098542791837</v>
+        <v>23.71828068391837</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1070462591878571</v>
+        <v>0.1076844649862564</v>
       </c>
       <c r="T24">
-        <v>1.032699917606684</v>
+        <v>1.043460984227937</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.039483690859565</v>
+        <v>6.733419182561322</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09240867803941742</v>
+        <v>0.09224231391230628</v>
       </c>
       <c r="C25">
-        <v>276.0788684549348</v>
+        <v>273.8216569505775</v>
       </c>
       <c r="D25">
-        <v>335.2128684549348</v>
+        <v>336.4136569505775</v>
       </c>
       <c r="E25">
-        <v>-8.465999999999994</v>
+        <v>-5.007999999999996</v>
       </c>
       <c r="F25">
-        <v>79.53400000000001</v>
+        <v>82.992</v>
       </c>
       <c r="G25">
         <v>20.4</v>
@@ -3468,28 +3468,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M25">
-        <v>4.318696200000001</v>
+        <v>4.5064656</v>
       </c>
       <c r="N25">
-        <v>24.76089563673469</v>
+        <v>24.57312623673469</v>
       </c>
       <c r="O25">
-        <v>5.942614952816326</v>
+        <v>5.897550296816326</v>
       </c>
       <c r="P25">
-        <v>18.81828068391837</v>
+        <v>18.67557593991837</v>
       </c>
       <c r="Q25">
-        <v>23.71828068391837</v>
+        <v>23.57557593991837</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1076844649862564</v>
+        <v>0.1083394656740872</v>
       </c>
       <c r="T25">
-        <v>1.043460984227937</v>
+        <v>1.054505236812906</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.733419182561322</v>
+        <v>6.452860049954602</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09224231391230626</v>
+        <v>0.09207594978519515</v>
       </c>
       <c r="C26">
-        <v>273.8216569505776</v>
+        <v>271.5730792238455</v>
       </c>
       <c r="D26">
-        <v>336.4136569505776</v>
+        <v>337.6230792238455</v>
       </c>
       <c r="E26">
-        <v>-5.007999999999996</v>
+        <v>-1.549999999999997</v>
       </c>
       <c r="F26">
-        <v>82.992</v>
+        <v>86.45</v>
       </c>
       <c r="G26">
         <v>20.4</v>
@@ -3550,28 +3550,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M26">
-        <v>4.5064656</v>
+        <v>4.694235</v>
       </c>
       <c r="N26">
-        <v>24.57312623673469</v>
+        <v>24.38535683673469</v>
       </c>
       <c r="O26">
-        <v>5.897550296816326</v>
+        <v>5.852485640816326</v>
       </c>
       <c r="P26">
-        <v>18.67557593991837</v>
+        <v>18.53287119591837</v>
       </c>
       <c r="Q26">
-        <v>23.57557593991837</v>
+        <v>23.43287119591837</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1083394656740872</v>
+        <v>0.1090119330469269</v>
       </c>
       <c r="T26">
-        <v>1.054505236812906</v>
+        <v>1.065844002800142</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.452860049954602</v>
+        <v>6.194745647956418</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09207594978519515</v>
+        <v>0.092107185658084</v>
       </c>
       <c r="C27">
-        <v>271.5730792238455</v>
+        <v>267.8873402361029</v>
       </c>
       <c r="D27">
-        <v>337.6230792238455</v>
+        <v>337.395340236103</v>
       </c>
       <c r="E27">
-        <v>-1.549999999999997</v>
+        <v>1.908000000000001</v>
       </c>
       <c r="F27">
-        <v>86.45</v>
+        <v>89.908</v>
       </c>
       <c r="G27">
         <v>20.4</v>
@@ -3632,45 +3632,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M27">
-        <v>4.694235</v>
+        <v>4.9719124</v>
       </c>
       <c r="N27">
-        <v>24.38535683673469</v>
+        <v>24.10767943673469</v>
       </c>
       <c r="O27">
-        <v>5.852485640816326</v>
+        <v>5.785843064816325</v>
       </c>
       <c r="P27">
-        <v>18.53287119591837</v>
+        <v>18.32183637191837</v>
       </c>
       <c r="Q27">
-        <v>23.43287119591837</v>
+        <v>23.22183637191836</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1090119330469269</v>
+        <v>0.109702575213627</v>
       </c>
       <c r="T27">
-        <v>1.065844002800142</v>
+        <v>1.077489221922167</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.24</v>
       </c>
       <c r="W27">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.194745647956418</v>
+        <v>5.84877397211075</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.092107185658084</v>
+        <v>0.09194842153097287</v>
       </c>
       <c r="C28">
-        <v>267.8873402361029</v>
+        <v>265.5900793233109</v>
       </c>
       <c r="D28">
-        <v>337.395340236103</v>
+        <v>338.5560793233109</v>
       </c>
       <c r="E28">
-        <v>1.908000000000001</v>
+        <v>5.366000000000014</v>
       </c>
       <c r="F28">
-        <v>89.908</v>
+        <v>93.36600000000001</v>
       </c>
       <c r="G28">
         <v>20.4</v>
@@ -3714,28 +3714,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M28">
-        <v>4.9719124</v>
+        <v>5.163139800000001</v>
       </c>
       <c r="N28">
-        <v>24.10767943673469</v>
+        <v>23.91645203673469</v>
       </c>
       <c r="O28">
-        <v>5.785843064816325</v>
+        <v>5.739948488816326</v>
       </c>
       <c r="P28">
-        <v>18.32183637191837</v>
+        <v>18.17650354791837</v>
       </c>
       <c r="Q28">
-        <v>23.22183637191836</v>
+        <v>23.07650354791836</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.109702575213627</v>
+        <v>0.1104121390835245</v>
       </c>
       <c r="T28">
-        <v>1.077489221922167</v>
+        <v>1.089453488143427</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.84877397211075</v>
+        <v>5.632152713884426</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09194842153097287</v>
+        <v>0.09178965740386173</v>
       </c>
       <c r="C29">
-        <v>265.5900793233109</v>
+        <v>263.3008325484093</v>
       </c>
       <c r="D29">
-        <v>338.5560793233109</v>
+        <v>339.7248325484093</v>
       </c>
       <c r="E29">
-        <v>5.366000000000014</v>
+        <v>8.824000000000012</v>
       </c>
       <c r="F29">
-        <v>93.36600000000001</v>
+        <v>96.82400000000001</v>
       </c>
       <c r="G29">
         <v>20.4</v>
@@ -3796,28 +3796,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M29">
-        <v>5.163139800000001</v>
+        <v>5.3543672</v>
       </c>
       <c r="N29">
-        <v>23.91645203673469</v>
+        <v>23.72522463673469</v>
       </c>
       <c r="O29">
-        <v>5.739948488816326</v>
+        <v>5.694053912816327</v>
       </c>
       <c r="P29">
-        <v>18.17650354791837</v>
+        <v>18.03117072391837</v>
       </c>
       <c r="Q29">
-        <v>23.07650354791836</v>
+        <v>22.93117072391837</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1104121390835245</v>
+        <v>0.1111414130609191</v>
       </c>
       <c r="T29">
-        <v>1.089453488143427</v>
+        <v>1.101750095093054</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.632152713884426</v>
+        <v>5.431004402674268</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09178965740386173</v>
+        <v>0.0916308932767506</v>
       </c>
       <c r="C30">
-        <v>263.3008325484093</v>
+        <v>261.0196831974208</v>
       </c>
       <c r="D30">
-        <v>339.7248325484093</v>
+        <v>340.9016831974208</v>
       </c>
       <c r="E30">
-        <v>8.824000000000012</v>
+        <v>12.28200000000001</v>
       </c>
       <c r="F30">
-        <v>96.82400000000001</v>
+        <v>100.282</v>
       </c>
       <c r="G30">
         <v>20.4</v>
@@ -3878,28 +3878,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M30">
-        <v>5.3543672</v>
+        <v>5.545594600000001</v>
       </c>
       <c r="N30">
-        <v>23.72522463673469</v>
+        <v>23.53399723673469</v>
       </c>
       <c r="O30">
-        <v>5.694053912816327</v>
+        <v>5.648159336816326</v>
       </c>
       <c r="P30">
-        <v>18.03117072391837</v>
+        <v>17.88583789991836</v>
       </c>
       <c r="Q30">
-        <v>22.93117072391837</v>
+        <v>22.78583789991836</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1111414130609191</v>
+        <v>0.1118912299672544</v>
       </c>
       <c r="T30">
-        <v>1.101750095093054</v>
+        <v>1.114393085337038</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.431004402674268</v>
+        <v>5.243728388788948</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0916308932767506</v>
+        <v>0.09147212914963945</v>
       </c>
       <c r="C31">
-        <v>261.0196831974208</v>
+        <v>258.7467157144343</v>
       </c>
       <c r="D31">
-        <v>340.9016831974208</v>
+        <v>342.0867157144343</v>
       </c>
       <c r="E31">
-        <v>12.282</v>
+        <v>15.73999999999999</v>
       </c>
       <c r="F31">
-        <v>100.282</v>
+        <v>103.74</v>
       </c>
       <c r="G31">
         <v>20.4</v>
@@ -3960,28 +3960,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M31">
-        <v>5.5455946</v>
+        <v>5.736822</v>
       </c>
       <c r="N31">
-        <v>23.53399723673469</v>
+        <v>23.34276983673469</v>
       </c>
       <c r="O31">
-        <v>5.648159336816326</v>
+        <v>5.602264760816326</v>
       </c>
       <c r="P31">
-        <v>17.88583789991836</v>
+        <v>17.74050507591837</v>
       </c>
       <c r="Q31">
-        <v>22.78583789991836</v>
+        <v>22.64050507591837</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1118912299672544</v>
+        <v>0.1126624702137707</v>
       </c>
       <c r="T31">
-        <v>1.114393085337038</v>
+        <v>1.127397303873706</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.243728388788948</v>
+        <v>5.068937442495983</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09147212914963945</v>
+        <v>0.09131336502252833</v>
       </c>
       <c r="C32">
-        <v>258.7467157144343</v>
+        <v>256.482015721802</v>
       </c>
       <c r="D32">
-        <v>342.0867157144343</v>
+        <v>343.280015721802</v>
       </c>
       <c r="E32">
-        <v>15.73999999999999</v>
+        <v>19.19800000000001</v>
       </c>
       <c r="F32">
-        <v>103.74</v>
+        <v>107.198</v>
       </c>
       <c r="G32">
         <v>20.4</v>
@@ -4042,28 +4042,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M32">
-        <v>5.736822</v>
+        <v>5.928049400000001</v>
       </c>
       <c r="N32">
-        <v>23.34276983673469</v>
+        <v>23.15154243673469</v>
       </c>
       <c r="O32">
-        <v>5.602264760816326</v>
+        <v>5.556370184816326</v>
       </c>
       <c r="P32">
-        <v>17.74050507591837</v>
+        <v>17.59517225191837</v>
       </c>
       <c r="Q32">
-        <v>22.64050507591837</v>
+        <v>22.49517225191837</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1126624702137707</v>
+        <v>0.1134560652500411</v>
       </c>
       <c r="T32">
-        <v>1.127397303873706</v>
+        <v>1.140778456281003</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.068937442495983</v>
+        <v>4.905423331447725</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09131336502252833</v>
+        <v>0.09115460089541719</v>
       </c>
       <c r="C33">
-        <v>256.482015721802</v>
+        <v>254.2256700407639</v>
       </c>
       <c r="D33">
-        <v>343.280015721802</v>
+        <v>344.481670040764</v>
       </c>
       <c r="E33">
-        <v>19.19800000000001</v>
+        <v>22.65600000000001</v>
       </c>
       <c r="F33">
-        <v>107.198</v>
+        <v>110.656</v>
       </c>
       <c r="G33">
         <v>20.4</v>
@@ -4124,28 +4124,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M33">
-        <v>5.928049400000001</v>
+        <v>6.119276800000001</v>
       </c>
       <c r="N33">
-        <v>23.15154243673469</v>
+        <v>22.96031503673469</v>
       </c>
       <c r="O33">
-        <v>5.556370184816326</v>
+        <v>5.510475608816326</v>
       </c>
       <c r="P33">
-        <v>17.59517225191837</v>
+        <v>17.44983942791837</v>
       </c>
       <c r="Q33">
-        <v>22.49517225191837</v>
+        <v>22.34983942791836</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1134560652500411</v>
+        <v>0.11427300131679</v>
       </c>
       <c r="T33">
-        <v>1.140778456281003</v>
+        <v>1.154553171994396</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.905423331447725</v>
+        <v>4.752128852339984</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09115460089541719</v>
+        <v>0.09099583676830605</v>
       </c>
       <c r="C34">
-        <v>254.2256700407639</v>
+        <v>251.9777667125033</v>
       </c>
       <c r="D34">
-        <v>344.481670040764</v>
+        <v>345.6917667125034</v>
       </c>
       <c r="E34">
-        <v>22.65600000000001</v>
+        <v>26.114</v>
       </c>
       <c r="F34">
-        <v>110.656</v>
+        <v>114.114</v>
       </c>
       <c r="G34">
         <v>20.4</v>
@@ -4206,28 +4206,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M34">
-        <v>6.119276800000001</v>
+        <v>6.3105042</v>
       </c>
       <c r="N34">
-        <v>22.96031503673469</v>
+        <v>22.76908763673469</v>
       </c>
       <c r="O34">
-        <v>5.510475608816326</v>
+        <v>5.464581032816326</v>
       </c>
       <c r="P34">
-        <v>17.44983942791837</v>
+        <v>17.30450660391837</v>
       </c>
       <c r="Q34">
-        <v>22.34983942791836</v>
+        <v>22.20450660391836</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.11427300131679</v>
+        <v>0.1151143235347852</v>
       </c>
       <c r="T34">
-        <v>1.154553171994396</v>
+        <v>1.168739073251473</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.752128852339984</v>
+        <v>4.608124947723621</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09099583676830605</v>
+        <v>0.09148307264119492</v>
       </c>
       <c r="C35">
-        <v>251.9777667125033</v>
+        <v>244.8327680067119</v>
       </c>
       <c r="D35">
-        <v>345.6917667125034</v>
+        <v>342.004768006712</v>
       </c>
       <c r="E35">
-        <v>26.114</v>
+        <v>29.57200000000002</v>
       </c>
       <c r="F35">
-        <v>114.114</v>
+        <v>117.572</v>
       </c>
       <c r="G35">
         <v>20.4</v>
@@ -4288,45 +4288,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M35">
-        <v>6.3105042</v>
+        <v>6.795661600000002</v>
       </c>
       <c r="N35">
-        <v>22.76908763673469</v>
+        <v>22.28393023673469</v>
       </c>
       <c r="O35">
-        <v>5.464581032816326</v>
+        <v>5.348143256816326</v>
       </c>
       <c r="P35">
-        <v>17.30450660391837</v>
+        <v>16.93578697991837</v>
       </c>
       <c r="Q35">
-        <v>22.20450660391836</v>
+        <v>21.83578697991836</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1151143235347852</v>
+        <v>0.1159811403654468</v>
       </c>
       <c r="T35">
-        <v>1.168739073251473</v>
+        <v>1.183354850304219</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.608124947723621</v>
+        <v>4.279140655964194</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09148307264119492</v>
+        <v>0.09134330851408377</v>
       </c>
       <c r="C36">
-        <v>244.8327680067119</v>
+        <v>242.424318411104</v>
       </c>
       <c r="D36">
-        <v>342.004768006712</v>
+        <v>343.054318411104</v>
       </c>
       <c r="E36">
-        <v>29.57200000000002</v>
+        <v>33.03000000000002</v>
       </c>
       <c r="F36">
-        <v>117.572</v>
+        <v>121.03</v>
       </c>
       <c r="G36">
         <v>20.4</v>
@@ -4370,28 +4370,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M36">
-        <v>6.795661600000002</v>
+        <v>6.995534000000001</v>
       </c>
       <c r="N36">
-        <v>22.28393023673469</v>
+        <v>22.08405783673469</v>
       </c>
       <c r="O36">
-        <v>5.348143256816326</v>
+        <v>5.300173880816327</v>
       </c>
       <c r="P36">
-        <v>16.93578697991837</v>
+        <v>16.78388395591837</v>
       </c>
       <c r="Q36">
-        <v>21.83578697991836</v>
+        <v>21.68388395591836</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1159811403654468</v>
+        <v>0.1168746284832058</v>
       </c>
       <c r="T36">
-        <v>1.183354850304219</v>
+        <v>1.198420343573973</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.279140655964194</v>
+        <v>4.156879494365218</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09134330851408377</v>
+        <v>0.09120354438697265</v>
       </c>
       <c r="C37">
-        <v>242.424318411104</v>
+        <v>240.0223304033789</v>
       </c>
       <c r="D37">
-        <v>343.054318411104</v>
+        <v>344.1103304033789</v>
       </c>
       <c r="E37">
-        <v>33.03000000000002</v>
+        <v>36.48800000000001</v>
       </c>
       <c r="F37">
-        <v>121.03</v>
+        <v>124.488</v>
       </c>
       <c r="G37">
         <v>20.4</v>
@@ -4452,28 +4452,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M37">
-        <v>6.995534000000001</v>
+        <v>7.195406400000001</v>
       </c>
       <c r="N37">
-        <v>22.08405783673469</v>
+        <v>21.88418543673469</v>
       </c>
       <c r="O37">
-        <v>5.300173880816327</v>
+        <v>5.252204504816326</v>
       </c>
       <c r="P37">
-        <v>16.78388395591837</v>
+        <v>16.63198093191836</v>
       </c>
       <c r="Q37">
-        <v>21.68388395591836</v>
+        <v>21.53198093191836</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1168746284832058</v>
+        <v>0.1177960381046448</v>
       </c>
       <c r="T37">
-        <v>1.198420343573973</v>
+        <v>1.213956633508406</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.156879494365218</v>
+        <v>4.04141061952174</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09120354438697265</v>
+        <v>0.09204798025986151</v>
       </c>
       <c r="C38">
-        <v>240.0223304033789</v>
+        <v>230.2812645139817</v>
       </c>
       <c r="D38">
-        <v>344.1103304033789</v>
+        <v>337.8272645139817</v>
       </c>
       <c r="E38">
-        <v>36.488</v>
+        <v>39.946</v>
       </c>
       <c r="F38">
-        <v>124.488</v>
+        <v>127.946</v>
       </c>
       <c r="G38">
         <v>20.4</v>
@@ -4534,45 +4534,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M38">
-        <v>7.1954064</v>
+        <v>7.8430898</v>
       </c>
       <c r="N38">
-        <v>21.88418543673469</v>
+        <v>21.23650203673469</v>
       </c>
       <c r="O38">
-        <v>5.252204504816326</v>
+        <v>5.096760488816326</v>
       </c>
       <c r="P38">
-        <v>16.63198093191837</v>
+        <v>16.13974154791837</v>
       </c>
       <c r="Q38">
-        <v>21.53198093191837</v>
+        <v>21.03974154791836</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1177960381046448</v>
+        <v>0.118746698825177</v>
       </c>
       <c r="T38">
-        <v>1.213956633508406</v>
+        <v>1.229986138996313</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.24</v>
       </c>
       <c r="W38">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.04141061952174</v>
+        <v>3.707670392443383</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09204798025986151</v>
+        <v>0.09193481613275037</v>
       </c>
       <c r="C39">
-        <v>230.2812645139817</v>
+        <v>227.6519212792555</v>
       </c>
       <c r="D39">
-        <v>337.8272645139817</v>
+        <v>338.6559212792556</v>
       </c>
       <c r="E39">
-        <v>39.946</v>
+        <v>43.404</v>
       </c>
       <c r="F39">
-        <v>127.946</v>
+        <v>131.404</v>
       </c>
       <c r="G39">
         <v>20.4</v>
@@ -4616,28 +4616,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M39">
-        <v>7.8430898</v>
+        <v>8.0550652</v>
       </c>
       <c r="N39">
-        <v>21.23650203673469</v>
+        <v>21.02452663673469</v>
       </c>
       <c r="O39">
-        <v>5.096760488816326</v>
+        <v>5.045886392816326</v>
       </c>
       <c r="P39">
-        <v>16.13974154791837</v>
+        <v>15.97864024391837</v>
       </c>
       <c r="Q39">
-        <v>21.03974154791836</v>
+        <v>20.87864024391837</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.118746698825177</v>
+        <v>0.1197280260205651</v>
       </c>
       <c r="T39">
-        <v>1.229986138996313</v>
+        <v>1.246532725306412</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.707670392443383</v>
+        <v>3.610100118958031</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09193481613275037</v>
+        <v>0.09182165200563924</v>
       </c>
       <c r="C40">
-        <v>227.6519212792555</v>
+        <v>225.0266532663186</v>
       </c>
       <c r="D40">
-        <v>338.6559212792556</v>
+        <v>339.4886532663186</v>
       </c>
       <c r="E40">
-        <v>43.404</v>
+        <v>46.86200000000002</v>
       </c>
       <c r="F40">
-        <v>131.404</v>
+        <v>134.862</v>
       </c>
       <c r="G40">
         <v>20.4</v>
@@ -4698,28 +4698,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M40">
-        <v>8.0550652</v>
+        <v>8.267040600000001</v>
       </c>
       <c r="N40">
-        <v>21.02452663673469</v>
+        <v>20.81255123673469</v>
       </c>
       <c r="O40">
-        <v>5.045886392816326</v>
+        <v>4.995012296816326</v>
       </c>
       <c r="P40">
-        <v>15.97864024391837</v>
+        <v>15.81753893991836</v>
       </c>
       <c r="Q40">
-        <v>20.87864024391837</v>
+        <v>20.71753893991836</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1197280260205651</v>
+        <v>0.1207415278780971</v>
       </c>
       <c r="T40">
-        <v>1.246532725306412</v>
+        <v>1.26362182264307</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.610100118958031</v>
+        <v>3.517533449241157</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09182165200563924</v>
+        <v>0.0925596878785281</v>
       </c>
       <c r="C41">
-        <v>225.0266532663186</v>
+        <v>216.2103026032398</v>
       </c>
       <c r="D41">
-        <v>339.4886532663186</v>
+        <v>334.1303026032398</v>
       </c>
       <c r="E41">
-        <v>46.86200000000002</v>
+        <v>50.32000000000002</v>
       </c>
       <c r="F41">
-        <v>134.862</v>
+        <v>138.32</v>
       </c>
       <c r="G41">
         <v>20.4</v>
@@ -4780,45 +4780,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M41">
-        <v>8.267040600000001</v>
+        <v>8.866312000000002</v>
       </c>
       <c r="N41">
-        <v>20.81255123673469</v>
+        <v>20.21327983673469</v>
       </c>
       <c r="O41">
-        <v>4.995012296816326</v>
+        <v>4.851187160816326</v>
       </c>
       <c r="P41">
-        <v>15.81753893991836</v>
+        <v>15.36209267591837</v>
       </c>
       <c r="Q41">
-        <v>20.71753893991836</v>
+        <v>20.26209267591836</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1207415278780971</v>
+        <v>0.1217888131308802</v>
       </c>
       <c r="T41">
-        <v>1.26362182264307</v>
+        <v>1.281280556557617</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.24</v>
       </c>
       <c r="W41">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.517533449241157</v>
+        <v>3.279784406045567</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0925596878785281</v>
+        <v>0.09246780375141696</v>
       </c>
       <c r="C42">
-        <v>216.2103026032398</v>
+        <v>213.4101709563257</v>
       </c>
       <c r="D42">
-        <v>334.1303026032398</v>
+        <v>334.7881709563257</v>
       </c>
       <c r="E42">
-        <v>50.32000000000002</v>
+        <v>53.77800000000002</v>
       </c>
       <c r="F42">
-        <v>138.32</v>
+        <v>141.778</v>
       </c>
       <c r="G42">
         <v>20.4</v>
@@ -4862,28 +4862,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M42">
-        <v>8.866312000000002</v>
+        <v>9.087969800000002</v>
       </c>
       <c r="N42">
-        <v>20.21327983673469</v>
+        <v>19.99162203673469</v>
       </c>
       <c r="O42">
-        <v>4.851187160816326</v>
+        <v>4.797989288816325</v>
       </c>
       <c r="P42">
-        <v>15.36209267591837</v>
+        <v>15.19363274791836</v>
       </c>
       <c r="Q42">
-        <v>20.26209267591836</v>
+        <v>20.09363274791836</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1217888131308802</v>
+        <v>0.1228715995786728</v>
       </c>
       <c r="T42">
-        <v>1.281280556557617</v>
+        <v>1.29953789162181</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.279784406045567</v>
+        <v>3.1997896644347</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09246780375141696</v>
+        <v>0.09237591962430582</v>
       </c>
       <c r="C43">
-        <v>213.4101709563257</v>
+        <v>210.6126349708548</v>
       </c>
       <c r="D43">
-        <v>334.7881709563257</v>
+        <v>335.4486349708549</v>
       </c>
       <c r="E43">
-        <v>53.77800000000002</v>
+        <v>57.23600000000002</v>
       </c>
       <c r="F43">
-        <v>141.778</v>
+        <v>145.236</v>
       </c>
       <c r="G43">
         <v>20.4</v>
@@ -4944,28 +4944,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M43">
-        <v>9.087969800000002</v>
+        <v>9.309627600000002</v>
       </c>
       <c r="N43">
-        <v>19.99162203673469</v>
+        <v>19.76996423673469</v>
       </c>
       <c r="O43">
-        <v>4.797989288816325</v>
+        <v>4.744791416816326</v>
       </c>
       <c r="P43">
-        <v>15.19363274791836</v>
+        <v>15.02517281991836</v>
       </c>
       <c r="Q43">
-        <v>20.09363274791836</v>
+        <v>19.92517281991836</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1228715995786728</v>
+        <v>0.1239917234901824</v>
       </c>
       <c r="T43">
-        <v>1.29953789162181</v>
+        <v>1.318424789964079</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.1997896644347</v>
+        <v>3.123604196233873</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09237591962430583</v>
+        <v>0.0922840354971947</v>
       </c>
       <c r="C44">
-        <v>210.6126349708548</v>
+        <v>207.8177100392141</v>
       </c>
       <c r="D44">
-        <v>335.4486349708548</v>
+        <v>336.1117100392141</v>
       </c>
       <c r="E44">
-        <v>57.23599999999999</v>
+        <v>60.69399999999999</v>
       </c>
       <c r="F44">
-        <v>145.236</v>
+        <v>148.694</v>
       </c>
       <c r="G44">
         <v>20.4</v>
@@ -5026,28 +5026,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M44">
-        <v>9.309627600000001</v>
+        <v>9.5312854</v>
       </c>
       <c r="N44">
-        <v>19.76996423673469</v>
+        <v>19.54830643673469</v>
       </c>
       <c r="O44">
-        <v>4.744791416816327</v>
+        <v>4.691593544816326</v>
       </c>
       <c r="P44">
-        <v>15.02517281991837</v>
+        <v>14.85671289191837</v>
       </c>
       <c r="Q44">
-        <v>19.92517281991837</v>
+        <v>19.75671289191837</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1239917234901824</v>
+        <v>0.1251511499950784</v>
       </c>
       <c r="T44">
-        <v>1.318424789964078</v>
+        <v>1.337974386493795</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.123604196233874</v>
+        <v>3.050962238181924</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0922840354971947</v>
+        <v>0.09480047137008354</v>
       </c>
       <c r="C45">
-        <v>207.8177100392141</v>
+        <v>187.0985788543193</v>
       </c>
       <c r="D45">
-        <v>336.1117100392141</v>
+        <v>318.8505788543193</v>
       </c>
       <c r="E45">
-        <v>60.69399999999999</v>
+        <v>64.15200000000002</v>
       </c>
       <c r="F45">
-        <v>148.694</v>
+        <v>152.152</v>
       </c>
       <c r="G45">
         <v>20.4</v>
@@ -5108,45 +5108,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M45">
-        <v>9.5312854</v>
+        <v>10.9397288</v>
       </c>
       <c r="N45">
-        <v>19.54830643673469</v>
+        <v>18.13986303673469</v>
       </c>
       <c r="O45">
-        <v>4.691593544816326</v>
+        <v>4.353567128816325</v>
       </c>
       <c r="P45">
-        <v>14.85671289191837</v>
+        <v>13.78629590791836</v>
       </c>
       <c r="Q45">
-        <v>19.75671289191837</v>
+        <v>18.68629590791836</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1251511499950784</v>
+        <v>0.1263519845894349</v>
       </c>
       <c r="T45">
-        <v>1.337974386493795</v>
+        <v>1.358222182899573</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.050962238181924</v>
+        <v>2.658163869357957</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09480047137008354</v>
+        <v>0.09476786724297243</v>
       </c>
       <c r="C46">
-        <v>187.0985788543193</v>
+        <v>183.8528781719685</v>
       </c>
       <c r="D46">
-        <v>318.8505788543193</v>
+        <v>319.0628781719685</v>
       </c>
       <c r="E46">
-        <v>64.15200000000002</v>
+        <v>67.61000000000001</v>
       </c>
       <c r="F46">
-        <v>152.152</v>
+        <v>155.61</v>
       </c>
       <c r="G46">
         <v>20.4</v>
@@ -5190,28 +5190,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M46">
-        <v>10.9397288</v>
+        <v>11.188359</v>
       </c>
       <c r="N46">
-        <v>18.13986303673469</v>
+        <v>17.89123283673469</v>
       </c>
       <c r="O46">
-        <v>4.353567128816325</v>
+        <v>4.293895880816326</v>
       </c>
       <c r="P46">
-        <v>13.78629590791836</v>
+        <v>13.59733695591837</v>
       </c>
       <c r="Q46">
-        <v>18.68629590791836</v>
+        <v>18.49733695591836</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1263519845894349</v>
+        <v>0.1275964858963135</v>
       </c>
       <c r="T46">
-        <v>1.358222182899573</v>
+        <v>1.379206262811015</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.658163869357957</v>
+        <v>2.599093561150003</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09476786724297243</v>
+        <v>0.09473526311586128</v>
       </c>
       <c r="C47">
-        <v>183.8528781719685</v>
+        <v>180.6074603872053</v>
       </c>
       <c r="D47">
-        <v>319.0628781719685</v>
+        <v>319.2754603872053</v>
       </c>
       <c r="E47">
-        <v>67.61000000000001</v>
+        <v>71.06800000000001</v>
       </c>
       <c r="F47">
-        <v>155.61</v>
+        <v>159.068</v>
       </c>
       <c r="G47">
         <v>20.4</v>
@@ -5272,28 +5272,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M47">
-        <v>11.188359</v>
+        <v>11.4369892</v>
       </c>
       <c r="N47">
-        <v>17.89123283673469</v>
+        <v>17.64260263673469</v>
       </c>
       <c r="O47">
-        <v>4.293895880816326</v>
+        <v>4.234224632816327</v>
       </c>
       <c r="P47">
-        <v>13.59733695591837</v>
+        <v>13.40837800391837</v>
       </c>
       <c r="Q47">
-        <v>18.49733695591836</v>
+        <v>18.30837800391836</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1275964858963135</v>
+        <v>0.1288870798441875</v>
       </c>
       <c r="T47">
-        <v>1.379206262811015</v>
+        <v>1.400967530867326</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.599093561150003</v>
+        <v>2.54259152721196</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09473526311586128</v>
+        <v>0.09609573898875015</v>
       </c>
       <c r="C48">
-        <v>180.6074603872053</v>
+        <v>168.5132106890065</v>
       </c>
       <c r="D48">
-        <v>319.2754603872053</v>
+        <v>310.6392106890065</v>
       </c>
       <c r="E48">
-        <v>71.06800000000001</v>
+        <v>74.52600000000001</v>
       </c>
       <c r="F48">
-        <v>159.068</v>
+        <v>162.526</v>
       </c>
       <c r="G48">
         <v>20.4</v>
@@ -5354,45 +5354,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M48">
-        <v>11.4369892</v>
+        <v>12.3194708</v>
       </c>
       <c r="N48">
-        <v>17.64260263673469</v>
+        <v>16.76012103673469</v>
       </c>
       <c r="O48">
-        <v>4.234224632816327</v>
+        <v>4.022429048816326</v>
       </c>
       <c r="P48">
-        <v>13.40837800391837</v>
+        <v>12.73769198791837</v>
       </c>
       <c r="Q48">
-        <v>18.30837800391836</v>
+        <v>17.63769198791837</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1288870798441875</v>
+        <v>0.130226375450472</v>
       </c>
       <c r="T48">
-        <v>1.400967530867326</v>
+        <v>1.42354997885029</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.54259152721196</v>
+        <v>2.360457872649423</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09609573898875015</v>
+        <v>0.096092774861639</v>
       </c>
       <c r="C49">
-        <v>168.5132106890065</v>
+        <v>165.0735189670588</v>
       </c>
       <c r="D49">
-        <v>310.6392106890065</v>
+        <v>310.6575189670589</v>
       </c>
       <c r="E49">
-        <v>74.52600000000001</v>
+        <v>77.98400000000001</v>
       </c>
       <c r="F49">
-        <v>162.526</v>
+        <v>165.984</v>
       </c>
       <c r="G49">
         <v>20.4</v>
@@ -5436,28 +5436,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M49">
-        <v>12.3194708</v>
+        <v>12.5815872</v>
       </c>
       <c r="N49">
-        <v>16.76012103673469</v>
+        <v>16.49800463673469</v>
       </c>
       <c r="O49">
-        <v>4.022429048816326</v>
+        <v>3.959521112816326</v>
       </c>
       <c r="P49">
-        <v>12.73769198791837</v>
+        <v>12.53848352391837</v>
       </c>
       <c r="Q49">
-        <v>17.63769198791837</v>
+        <v>17.43848352391836</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.130226375450472</v>
+        <v>0.1316171824262289</v>
       </c>
       <c r="T49">
-        <v>1.42354997885029</v>
+        <v>1.447000982524906</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.360457872649423</v>
+        <v>2.311281666969227</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.096092774861639</v>
+        <v>0.09608981073452787</v>
       </c>
       <c r="C50">
-        <v>165.0735189670588</v>
+        <v>161.6338294033241</v>
       </c>
       <c r="D50">
-        <v>310.6575189670589</v>
+        <v>310.6758294033241</v>
       </c>
       <c r="E50">
-        <v>77.98400000000001</v>
+        <v>81.44200000000001</v>
       </c>
       <c r="F50">
-        <v>165.984</v>
+        <v>169.442</v>
       </c>
       <c r="G50">
         <v>20.4</v>
@@ -5518,28 +5518,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M50">
-        <v>12.5815872</v>
+        <v>12.8437036</v>
       </c>
       <c r="N50">
-        <v>16.49800463673469</v>
+        <v>16.23588823673469</v>
       </c>
       <c r="O50">
-        <v>3.959521112816326</v>
+        <v>3.896613176816326</v>
       </c>
       <c r="P50">
-        <v>12.53848352391837</v>
+        <v>12.33927505991837</v>
       </c>
       <c r="Q50">
-        <v>17.43848352391836</v>
+        <v>17.23927505991836</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1316171824262289</v>
+        <v>0.1330625308520154</v>
       </c>
       <c r="T50">
-        <v>1.447000982524906</v>
+        <v>1.471371633402448</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.311281666969227</v>
+        <v>2.26411265335761</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09608981073452787</v>
+        <v>0.09608684660741673</v>
       </c>
       <c r="C51">
-        <v>161.6338294033241</v>
+        <v>158.1941419981841</v>
       </c>
       <c r="D51">
-        <v>310.6758294033241</v>
+        <v>310.6941419981841</v>
       </c>
       <c r="E51">
-        <v>81.44200000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F51">
-        <v>169.442</v>
+        <v>172.9</v>
       </c>
       <c r="G51">
         <v>20.4</v>
@@ -5600,28 +5600,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M51">
-        <v>12.8437036</v>
+        <v>13.10582</v>
       </c>
       <c r="N51">
-        <v>16.23588823673469</v>
+        <v>15.97377183673469</v>
       </c>
       <c r="O51">
-        <v>3.896613176816326</v>
+        <v>3.833705240816326</v>
       </c>
       <c r="P51">
-        <v>12.33927505991837</v>
+        <v>12.14006659591837</v>
       </c>
       <c r="Q51">
-        <v>17.23927505991836</v>
+        <v>17.04006659591836</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1330625308520154</v>
+        <v>0.1345656932148335</v>
       </c>
       <c r="T51">
-        <v>1.471371633402448</v>
+        <v>1.496717110315093</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.26411265335761</v>
+        <v>2.218830400290458</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09608684660741673</v>
+        <v>0.0960838824803056</v>
       </c>
       <c r="C52">
-        <v>158.1941419981841</v>
+        <v>154.7544567520206</v>
       </c>
       <c r="D52">
-        <v>310.6941419981841</v>
+        <v>310.7124567520206</v>
       </c>
       <c r="E52">
-        <v>84.90000000000001</v>
+        <v>88.358</v>
       </c>
       <c r="F52">
-        <v>172.9</v>
+        <v>176.358</v>
       </c>
       <c r="G52">
         <v>20.4</v>
@@ -5682,28 +5682,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M52">
-        <v>13.10582</v>
+        <v>13.3679364</v>
       </c>
       <c r="N52">
-        <v>15.97377183673469</v>
+        <v>15.71165543673469</v>
       </c>
       <c r="O52">
-        <v>3.833705240816326</v>
+        <v>3.770797304816326</v>
       </c>
       <c r="P52">
-        <v>12.14006659591837</v>
+        <v>11.94085813191836</v>
       </c>
       <c r="Q52">
-        <v>17.04006659591836</v>
+        <v>16.84085813191836</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1345656932148335</v>
+        <v>0.1361302091434808</v>
       </c>
       <c r="T52">
-        <v>1.496717110315093</v>
+        <v>1.523097096489478</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.218830400290458</v>
+        <v>2.17532392185339</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0960838824803056</v>
+        <v>0.09608091835319446</v>
       </c>
       <c r="C53">
-        <v>154.7544567520206</v>
+        <v>151.3147736652153</v>
       </c>
       <c r="D53">
-        <v>310.7124567520206</v>
+        <v>310.7307736652153</v>
       </c>
       <c r="E53">
-        <v>88.358</v>
+        <v>91.816</v>
       </c>
       <c r="F53">
-        <v>176.358</v>
+        <v>179.816</v>
       </c>
       <c r="G53">
         <v>20.4</v>
@@ -5764,28 +5764,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M53">
-        <v>13.3679364</v>
+        <v>13.6300528</v>
       </c>
       <c r="N53">
-        <v>15.71165543673469</v>
+        <v>15.44953903673469</v>
       </c>
       <c r="O53">
-        <v>3.770797304816326</v>
+        <v>3.707889368816326</v>
       </c>
       <c r="P53">
-        <v>11.94085813191836</v>
+        <v>11.74164966791837</v>
       </c>
       <c r="Q53">
-        <v>16.84085813191836</v>
+        <v>16.64164966791837</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1361302091434808</v>
+        <v>0.1377599132358218</v>
       </c>
       <c r="T53">
-        <v>1.523097096489478</v>
+        <v>1.550576248754462</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.17532392185339</v>
+        <v>2.133490769510056</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09608091835319446</v>
+        <v>0.09607795422608333</v>
       </c>
       <c r="C54">
-        <v>151.3147736652153</v>
+        <v>147.8750927381502</v>
       </c>
       <c r="D54">
-        <v>310.7307736652153</v>
+        <v>310.7490927381502</v>
       </c>
       <c r="E54">
-        <v>91.816</v>
+        <v>95.27400000000003</v>
       </c>
       <c r="F54">
-        <v>179.816</v>
+        <v>183.274</v>
       </c>
       <c r="G54">
         <v>20.4</v>
@@ -5846,28 +5846,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M54">
-        <v>13.6300528</v>
+        <v>13.8921692</v>
       </c>
       <c r="N54">
-        <v>15.44953903673469</v>
+        <v>15.18742263673469</v>
       </c>
       <c r="O54">
-        <v>3.707889368816326</v>
+        <v>3.644981432816325</v>
       </c>
       <c r="P54">
-        <v>11.74164966791837</v>
+        <v>11.54244120391837</v>
       </c>
       <c r="Q54">
-        <v>16.64164966791837</v>
+        <v>16.44244120391836</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1377599132358218</v>
+        <v>0.1394589664384752</v>
       </c>
       <c r="T54">
-        <v>1.550576248754462</v>
+        <v>1.579224726647743</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.133490769510056</v>
+        <v>2.093236226689111</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09607795422608333</v>
+        <v>0.09607499009897219</v>
       </c>
       <c r="C55">
-        <v>147.8750927381502</v>
+        <v>144.4354139712073</v>
       </c>
       <c r="D55">
-        <v>310.7490927381502</v>
+        <v>310.7674139712073</v>
       </c>
       <c r="E55">
-        <v>95.27400000000003</v>
+        <v>98.73200000000003</v>
       </c>
       <c r="F55">
-        <v>183.274</v>
+        <v>186.732</v>
       </c>
       <c r="G55">
         <v>20.4</v>
@@ -5928,28 +5928,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M55">
-        <v>13.8921692</v>
+        <v>14.1542856</v>
       </c>
       <c r="N55">
-        <v>15.18742263673469</v>
+        <v>14.92530623673469</v>
       </c>
       <c r="O55">
-        <v>3.644981432816325</v>
+        <v>3.582073496816325</v>
       </c>
       <c r="P55">
-        <v>11.54244120391837</v>
+        <v>11.34323273991836</v>
       </c>
       <c r="Q55">
-        <v>16.44244120391836</v>
+        <v>16.24323273991836</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1394589664384752</v>
+        <v>0.1412318915195047</v>
       </c>
       <c r="T55">
-        <v>1.579224726647743</v>
+        <v>1.609118790536384</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.093236226689111</v>
+        <v>2.054472592861535</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09607499009897219</v>
+        <v>0.09607202597186107</v>
       </c>
       <c r="C56">
-        <v>144.4354139712073</v>
+        <v>140.9957373647685</v>
       </c>
       <c r="D56">
-        <v>310.7674139712073</v>
+        <v>310.7857373647686</v>
       </c>
       <c r="E56">
-        <v>98.73200000000003</v>
+        <v>102.19</v>
       </c>
       <c r="F56">
-        <v>186.732</v>
+        <v>190.19</v>
       </c>
       <c r="G56">
         <v>20.4</v>
@@ -6010,28 +6010,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M56">
-        <v>14.1542856</v>
+        <v>14.416402</v>
       </c>
       <c r="N56">
-        <v>14.92530623673469</v>
+        <v>14.66318983673469</v>
       </c>
       <c r="O56">
-        <v>3.582073496816325</v>
+        <v>3.519165560816325</v>
       </c>
       <c r="P56">
-        <v>11.34323273991836</v>
+        <v>11.14402427591836</v>
       </c>
       <c r="Q56">
-        <v>16.24323273991836</v>
+        <v>16.04402427591836</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1412318915195047</v>
+        <v>0.1430836132708024</v>
       </c>
       <c r="T56">
-        <v>1.609118790536384</v>
+        <v>1.640341479486743</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.054472592861535</v>
+        <v>2.017118545718598</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09607202597186107</v>
+        <v>0.1021125818447499</v>
       </c>
       <c r="C57">
-        <v>140.9957373647685</v>
+        <v>104.2002744115605</v>
       </c>
       <c r="D57">
-        <v>310.7857373647686</v>
+        <v>277.4482744115606</v>
       </c>
       <c r="E57">
-        <v>102.19</v>
+        <v>105.648</v>
       </c>
       <c r="F57">
-        <v>190.19</v>
+        <v>193.648</v>
       </c>
       <c r="G57">
         <v>20.4</v>
@@ -6092,45 +6092,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M57">
-        <v>14.416402</v>
+        <v>17.42832</v>
       </c>
       <c r="N57">
-        <v>14.66318983673469</v>
+        <v>11.65127183673469</v>
       </c>
       <c r="O57">
-        <v>3.519165560816325</v>
+        <v>2.796305240816325</v>
       </c>
       <c r="P57">
-        <v>11.14402427591836</v>
+        <v>8.854966595918365</v>
       </c>
       <c r="Q57">
-        <v>16.04402427591836</v>
+        <v>13.75496659591836</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1430836132708024</v>
+        <v>0.1450195041926134</v>
       </c>
       <c r="T57">
-        <v>1.640341479486743</v>
+        <v>1.672983381571209</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.017118545718598</v>
+        <v>1.668525241488261</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1021125818447499</v>
+        <v>0.1022175377176388</v>
       </c>
       <c r="C58">
-        <v>104.2002744115605</v>
+        <v>100.2261259407053</v>
       </c>
       <c r="D58">
-        <v>277.4482744115606</v>
+        <v>276.9321259407054</v>
       </c>
       <c r="E58">
-        <v>105.648</v>
+        <v>109.106</v>
       </c>
       <c r="F58">
-        <v>193.648</v>
+        <v>197.106</v>
       </c>
       <c r="G58">
         <v>20.4</v>
@@ -6174,28 +6174,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M58">
-        <v>17.42832</v>
+        <v>17.73954</v>
       </c>
       <c r="N58">
-        <v>11.65127183673469</v>
+        <v>11.34005183673469</v>
       </c>
       <c r="O58">
-        <v>2.796305240816325</v>
+        <v>2.721612440816326</v>
       </c>
       <c r="P58">
-        <v>8.854966595918365</v>
+        <v>8.618439395918365</v>
       </c>
       <c r="Q58">
-        <v>13.75496659591836</v>
+        <v>13.51843939591836</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1450195041926134</v>
+        <v>0.1470454365526483</v>
       </c>
       <c r="T58">
-        <v>1.672983381571209</v>
+        <v>1.707143511659604</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.668525241488261</v>
+        <v>1.639252868830572</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1022175377176388</v>
+        <v>0.1023224935905276</v>
       </c>
       <c r="C59">
-        <v>100.2261259407053</v>
+        <v>96.25389432842655</v>
       </c>
       <c r="D59">
-        <v>276.9321259407054</v>
+        <v>276.4178943284266</v>
       </c>
       <c r="E59">
-        <v>109.106</v>
+        <v>112.564</v>
       </c>
       <c r="F59">
-        <v>197.106</v>
+        <v>200.564</v>
       </c>
       <c r="G59">
         <v>20.4</v>
@@ -6256,28 +6256,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M59">
-        <v>17.73954</v>
+        <v>18.05076</v>
       </c>
       <c r="N59">
-        <v>11.34005183673469</v>
+        <v>11.02883183673469</v>
       </c>
       <c r="O59">
-        <v>2.721612440816326</v>
+        <v>2.646919640816326</v>
       </c>
       <c r="P59">
-        <v>8.618439395918365</v>
+        <v>8.381912195918366</v>
       </c>
       <c r="Q59">
-        <v>13.51843939591836</v>
+        <v>13.28191219591836</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1470454365526483</v>
+        <v>0.1491678418822087</v>
       </c>
       <c r="T59">
-        <v>1.707143511659604</v>
+        <v>1.74293031460935</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.639252868830572</v>
+        <v>1.610989888333493</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1023224935905276</v>
+        <v>0.1024274494634165</v>
       </c>
       <c r="C60">
-        <v>96.25389432842658</v>
+        <v>92.28356891634735</v>
       </c>
       <c r="D60">
-        <v>276.4178943284266</v>
+        <v>275.9055689163474</v>
       </c>
       <c r="E60">
-        <v>112.564</v>
+        <v>116.022</v>
       </c>
       <c r="F60">
-        <v>200.564</v>
+        <v>204.022</v>
       </c>
       <c r="G60">
         <v>20.4</v>
@@ -6338,28 +6338,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M60">
-        <v>18.05076</v>
+        <v>18.36198</v>
       </c>
       <c r="N60">
-        <v>11.02883183673469</v>
+        <v>10.71761183673469</v>
       </c>
       <c r="O60">
-        <v>2.646919640816326</v>
+        <v>2.572226840816326</v>
       </c>
       <c r="P60">
-        <v>8.381912195918366</v>
+        <v>8.145384995918366</v>
       </c>
       <c r="Q60">
-        <v>13.28191219591836</v>
+        <v>13.04538499591836</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1491678418822087</v>
+        <v>0.1513937791790646</v>
       </c>
       <c r="T60">
-        <v>1.74293031460935</v>
+        <v>1.780462815263963</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.610989888333493</v>
+        <v>1.583684974971909</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1024274494634165</v>
+        <v>0.1025324053363054</v>
       </c>
       <c r="C61">
-        <v>92.28356891634735</v>
+        <v>88.31513912496351</v>
       </c>
       <c r="D61">
-        <v>275.9055689163474</v>
+        <v>275.3951391249635</v>
       </c>
       <c r="E61">
-        <v>116.022</v>
+        <v>119.48</v>
       </c>
       <c r="F61">
-        <v>204.022</v>
+        <v>207.48</v>
       </c>
       <c r="G61">
         <v>20.4</v>
@@ -6420,28 +6420,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M61">
-        <v>18.36198</v>
+        <v>18.6732</v>
       </c>
       <c r="N61">
-        <v>10.71761183673469</v>
+        <v>10.4063918367347</v>
       </c>
       <c r="O61">
-        <v>2.572226840816326</v>
+        <v>2.497534040816327</v>
       </c>
       <c r="P61">
-        <v>8.145384995918366</v>
+        <v>7.908857795918369</v>
       </c>
       <c r="Q61">
-        <v>13.04538499591836</v>
+        <v>12.80885779591837</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1513937791790646</v>
+        <v>0.1537310133407634</v>
       </c>
       <c r="T61">
-        <v>1.780462815263963</v>
+        <v>1.819871940951306</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.583684974971909</v>
+        <v>1.557290225389044</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1025324053363054</v>
+        <v>0.1026373612091942</v>
       </c>
       <c r="C62">
-        <v>88.31513912496351</v>
+        <v>84.34859445291539</v>
       </c>
       <c r="D62">
-        <v>275.3951391249635</v>
+        <v>274.8865944529154</v>
       </c>
       <c r="E62">
-        <v>119.48</v>
+        <v>122.938</v>
       </c>
       <c r="F62">
-        <v>207.48</v>
+        <v>210.938</v>
       </c>
       <c r="G62">
         <v>20.4</v>
@@ -6502,28 +6502,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M62">
-        <v>18.6732</v>
+        <v>18.98442</v>
       </c>
       <c r="N62">
-        <v>10.4063918367347</v>
+        <v>10.0951718367347</v>
       </c>
       <c r="O62">
-        <v>2.497534040816327</v>
+        <v>2.422841240816327</v>
       </c>
       <c r="P62">
-        <v>7.908857795918369</v>
+        <v>7.672330595918369</v>
       </c>
       <c r="Q62">
-        <v>12.80885779591837</v>
+        <v>12.57233059591837</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1537310133407634</v>
+        <v>0.1561881056646006</v>
       </c>
       <c r="T62">
-        <v>1.819871940951306</v>
+        <v>1.861302047443128</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.557290225389044</v>
+        <v>1.531760877431847</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1026373612091942</v>
+        <v>0.1027423170820831</v>
       </c>
       <c r="C63">
-        <v>84.34859445291539</v>
+        <v>80.38392447626751</v>
       </c>
       <c r="D63">
-        <v>274.8865944529154</v>
+        <v>274.3799244762675</v>
       </c>
       <c r="E63">
-        <v>122.938</v>
+        <v>126.396</v>
       </c>
       <c r="F63">
-        <v>210.938</v>
+        <v>214.396</v>
       </c>
       <c r="G63">
         <v>20.4</v>
@@ -6584,28 +6584,28 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M63">
-        <v>18.98442</v>
+        <v>19.29564</v>
       </c>
       <c r="N63">
-        <v>10.0951718367347</v>
+        <v>9.78395183673469</v>
       </c>
       <c r="O63">
-        <v>2.422841240816327</v>
+        <v>2.348148440816326</v>
       </c>
       <c r="P63">
-        <v>7.672330595918369</v>
+        <v>7.435803395918365</v>
       </c>
       <c r="Q63">
-        <v>12.57233059591837</v>
+        <v>12.33580339591836</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1561881056646006</v>
+        <v>0.1587745186370608</v>
       </c>
       <c r="T63">
-        <v>1.861302047443128</v>
+        <v>1.904912685855573</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.531760877431847</v>
+        <v>1.507055056828107</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1027423170820831</v>
+        <v>0.1327486171844998</v>
       </c>
       <c r="C64">
-        <v>80.38392447626751</v>
+        <v>-17.76363612298977</v>
       </c>
       <c r="D64">
-        <v>274.3799244762675</v>
+        <v>179.6903638770102</v>
       </c>
       <c r="E64">
-        <v>126.396</v>
+        <v>129.854</v>
       </c>
       <c r="F64">
-        <v>214.396</v>
+        <v>217.854</v>
       </c>
       <c r="G64">
         <v>20.4</v>
@@ -6666,45 +6666,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M64">
-        <v>19.29564</v>
+        <v>31.98096720000001</v>
       </c>
       <c r="N64">
-        <v>9.78395183673469</v>
+        <v>-2.901375363265313</v>
       </c>
       <c r="O64">
-        <v>2.348148440816326</v>
+        <v>-0.6963300871836751</v>
       </c>
       <c r="P64">
-        <v>7.435803395918365</v>
+        <v>-2.205045276081638</v>
       </c>
       <c r="Q64">
-        <v>12.33580339591836</v>
+        <v>2.694954723918361</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1587745186370608</v>
+        <v>0.1633705365014644</v>
       </c>
       <c r="T64">
-        <v>1.904912685855573</v>
+        <v>1.982408149787996</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.24</v>
+        <v>0.2182267345815709</v>
       </c>
       <c r="W64">
-        <v>0.0684</v>
+        <v>0.1147643153634254</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.507055056828107</v>
+        <v>0.9092780607565455</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1327486171844998</v>
+        <v>0.1337586171844998</v>
       </c>
       <c r="C65">
-        <v>-17.76363612298977</v>
+        <v>-23.28496173365846</v>
       </c>
       <c r="D65">
-        <v>179.6903638770102</v>
+        <v>177.6270382663415</v>
       </c>
       <c r="E65">
-        <v>129.854</v>
+        <v>133.312</v>
       </c>
       <c r="F65">
-        <v>217.854</v>
+        <v>221.312</v>
       </c>
       <c r="G65">
         <v>20.4</v>
@@ -6748,37 +6748,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M65">
-        <v>31.98096720000001</v>
+        <v>32.4886016</v>
       </c>
       <c r="N65">
-        <v>-2.901375363265313</v>
+        <v>-3.40900976326531</v>
       </c>
       <c r="O65">
-        <v>-0.6963300871836751</v>
+        <v>-0.8181623431836743</v>
       </c>
       <c r="P65">
-        <v>-2.205045276081638</v>
+        <v>-2.590847420081635</v>
       </c>
       <c r="Q65">
-        <v>2.694954723918361</v>
+        <v>2.309152579918363</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1633705365014644</v>
+        <v>0.1666363847376162</v>
       </c>
       <c r="T65">
-        <v>1.982408149787996</v>
+        <v>2.037475042837663</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2182267345815709</v>
+        <v>0.2148169418537339</v>
       </c>
       <c r="W65">
-        <v>0.1147643153634254</v>
+        <v>0.1152648729358719</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9092780607565455</v>
+        <v>0.8950705910572245</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1337586171844998</v>
+        <v>0.1347686171844998</v>
       </c>
       <c r="C66">
-        <v>-23.28496173365846</v>
+        <v>-28.75944028897834</v>
       </c>
       <c r="D66">
-        <v>177.6270382663415</v>
+        <v>175.6105597110217</v>
       </c>
       <c r="E66">
-        <v>133.312</v>
+        <v>136.77</v>
       </c>
       <c r="F66">
-        <v>221.312</v>
+        <v>224.77</v>
       </c>
       <c r="G66">
         <v>20.4</v>
@@ -6830,37 +6830,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M66">
-        <v>32.4886016</v>
+        <v>32.996236</v>
       </c>
       <c r="N66">
-        <v>-3.40900976326531</v>
+        <v>-3.91664416326531</v>
       </c>
       <c r="O66">
-        <v>-0.8181623431836743</v>
+        <v>-0.9399945991836745</v>
       </c>
       <c r="P66">
-        <v>-2.590847420081635</v>
+        <v>-2.976649564081636</v>
       </c>
       <c r="Q66">
-        <v>2.309152579918363</v>
+        <v>1.923350435918363</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1666363847376162</v>
+        <v>0.1700888528729767</v>
       </c>
       <c r="T66">
-        <v>2.037475042837663</v>
+        <v>2.095688615490168</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2148169418537339</v>
+        <v>0.2115120658252149</v>
       </c>
       <c r="W66">
-        <v>0.1152648729358719</v>
+        <v>0.1157500287368585</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8950705910572245</v>
+        <v>0.8813002742717287</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1347686171844998</v>
+        <v>0.1357786171844999</v>
       </c>
       <c r="C67">
-        <v>-28.75944028897834</v>
+        <v>-34.1886493479534</v>
       </c>
       <c r="D67">
-        <v>175.6105597110217</v>
+        <v>173.6393506520466</v>
       </c>
       <c r="E67">
-        <v>136.77</v>
+        <v>140.228</v>
       </c>
       <c r="F67">
-        <v>224.77</v>
+        <v>228.228</v>
       </c>
       <c r="G67">
         <v>20.4</v>
@@ -6912,37 +6912,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M67">
-        <v>32.996236</v>
+        <v>33.5038704</v>
       </c>
       <c r="N67">
-        <v>-3.91664416326531</v>
+        <v>-4.424278563265311</v>
       </c>
       <c r="O67">
-        <v>-0.9399945991836745</v>
+        <v>-1.061826855183675</v>
       </c>
       <c r="P67">
-        <v>-2.976649564081636</v>
+        <v>-3.362451708081636</v>
       </c>
       <c r="Q67">
-        <v>1.923350435918363</v>
+        <v>1.537548291918363</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1700888528729767</v>
+        <v>0.1737444073692407</v>
       </c>
       <c r="T67">
-        <v>2.095688615490168</v>
+        <v>2.157326515945761</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2115120658252149</v>
+        <v>0.2083073375551359</v>
       </c>
       <c r="W67">
-        <v>0.1157500287368585</v>
+        <v>0.1162204828469061</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8813002742717287</v>
+        <v>0.8679472398130662</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1357786171844999</v>
+        <v>0.1367886171844998</v>
       </c>
       <c r="C68">
-        <v>-34.1886493479534</v>
+        <v>-39.57409642414041</v>
       </c>
       <c r="D68">
-        <v>173.6393506520466</v>
+        <v>171.7119035758596</v>
       </c>
       <c r="E68">
-        <v>140.228</v>
+        <v>143.686</v>
       </c>
       <c r="F68">
-        <v>228.228</v>
+        <v>231.686</v>
       </c>
       <c r="G68">
         <v>20.4</v>
@@ -6994,37 +6994,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M68">
-        <v>33.5038704</v>
+        <v>34.01150480000001</v>
       </c>
       <c r="N68">
-        <v>-4.424278563265311</v>
+        <v>-4.931912963265319</v>
       </c>
       <c r="O68">
-        <v>-1.061826855183675</v>
+        <v>-1.183659111183677</v>
       </c>
       <c r="P68">
-        <v>-3.362451708081636</v>
+        <v>-3.748253852081642</v>
       </c>
       <c r="Q68">
-        <v>1.537548291918363</v>
+        <v>1.151746147918356</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1737444073692407</v>
+        <v>0.1776215106228541</v>
       </c>
       <c r="T68">
-        <v>2.157326515945761</v>
+        <v>2.222700046731997</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2083073375551359</v>
+        <v>0.2051982728155069</v>
       </c>
       <c r="W68">
-        <v>0.1162204828469061</v>
+        <v>0.1166768935506836</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8679472398130662</v>
+        <v>0.8549928033979456</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1367886171844998</v>
+        <v>0.1377986171844998</v>
       </c>
       <c r="C69">
-        <v>-39.57409642414041</v>
+        <v>-44.91722283059298</v>
       </c>
       <c r="D69">
-        <v>171.7119035758596</v>
+        <v>169.8267771694071</v>
       </c>
       <c r="E69">
-        <v>143.686</v>
+        <v>147.144</v>
       </c>
       <c r="F69">
-        <v>231.686</v>
+        <v>235.144</v>
       </c>
       <c r="G69">
         <v>20.4</v>
@@ -7076,37 +7076,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M69">
-        <v>34.01150480000001</v>
+        <v>34.51913920000001</v>
       </c>
       <c r="N69">
-        <v>-4.931912963265319</v>
+        <v>-5.439547363265312</v>
       </c>
       <c r="O69">
-        <v>-1.183659111183677</v>
+        <v>-1.305491367183675</v>
       </c>
       <c r="P69">
-        <v>-3.748253852081642</v>
+        <v>-4.134055996081637</v>
       </c>
       <c r="Q69">
-        <v>1.151746147918356</v>
+        <v>0.7659440039183618</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1776215106228541</v>
+        <v>0.1817409328298182</v>
       </c>
       <c r="T69">
-        <v>2.222700046731997</v>
+        <v>2.292159423192371</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2051982728155069</v>
+        <v>0.2021806511564554</v>
       </c>
       <c r="W69">
-        <v>0.1166768935506836</v>
+        <v>0.1171198804102324</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8549928033979456</v>
+        <v>0.8424193798185642</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1377986171844998</v>
+        <v>0.1388086171844998</v>
       </c>
       <c r="C70">
-        <v>-44.91722283059298</v>
+        <v>-50.21940727428645</v>
       </c>
       <c r="D70">
-        <v>169.8267771694071</v>
+        <v>167.9825927257136</v>
       </c>
       <c r="E70">
-        <v>147.144</v>
+        <v>150.602</v>
       </c>
       <c r="F70">
-        <v>235.144</v>
+        <v>238.602</v>
       </c>
       <c r="G70">
         <v>20.4</v>
@@ -7158,37 +7158,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M70">
-        <v>34.51913920000001</v>
+        <v>35.02677360000001</v>
       </c>
       <c r="N70">
-        <v>-5.439547363265312</v>
+        <v>-5.947181763265313</v>
       </c>
       <c r="O70">
-        <v>-1.305491367183675</v>
+        <v>-1.427323623183675</v>
       </c>
       <c r="P70">
-        <v>-4.134055996081637</v>
+        <v>-4.519858140081638</v>
       </c>
       <c r="Q70">
-        <v>0.7659440039183618</v>
+        <v>0.3801418599183606</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1817409328298182</v>
+        <v>0.1861261242114253</v>
       </c>
       <c r="T70">
-        <v>2.292159423192371</v>
+        <v>2.366100049746964</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2021806511564554</v>
+        <v>0.1992504967918691</v>
       </c>
       <c r="W70">
-        <v>0.1171198804102324</v>
+        <v>0.1175500270709536</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8424193798185642</v>
+        <v>0.8302104032994546</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1388086171844998</v>
+        <v>0.1398186171844998</v>
       </c>
       <c r="C71">
-        <v>-50.21940727428645</v>
+        <v>-55.48196921886421</v>
       </c>
       <c r="D71">
-        <v>167.9825927257136</v>
+        <v>166.1780307811358</v>
       </c>
       <c r="E71">
-        <v>150.602</v>
+        <v>154.06</v>
       </c>
       <c r="F71">
-        <v>238.602</v>
+        <v>242.06</v>
       </c>
       <c r="G71">
         <v>20.4</v>
@@ -7240,37 +7240,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M71">
-        <v>35.02677360000001</v>
+        <v>35.53440800000001</v>
       </c>
       <c r="N71">
-        <v>-5.947181763265313</v>
+        <v>-6.454816163265313</v>
       </c>
       <c r="O71">
-        <v>-1.427323623183675</v>
+        <v>-1.549155879183675</v>
       </c>
       <c r="P71">
-        <v>-4.519858140081638</v>
+        <v>-4.905660284081638</v>
       </c>
       <c r="Q71">
-        <v>0.3801418599183606</v>
+        <v>-0.005660284081639766</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1861261242114253</v>
+        <v>0.1908036616851395</v>
       </c>
       <c r="T71">
-        <v>2.366100049746964</v>
+        <v>2.444970051405196</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1992504967918691</v>
+        <v>0.1964040611234138</v>
       </c>
       <c r="W71">
-        <v>0.1175500270709536</v>
+        <v>0.1179678838270829</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8302104032994546</v>
+        <v>0.818350254680891</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1398186171844998</v>
+        <v>0.1408286171844998</v>
       </c>
       <c r="C72">
-        <v>-55.48196921886421</v>
+        <v>-60.70617203293952</v>
       </c>
       <c r="D72">
-        <v>166.1780307811358</v>
+        <v>164.4118279670605</v>
       </c>
       <c r="E72">
-        <v>154.06</v>
+        <v>157.518</v>
       </c>
       <c r="F72">
-        <v>242.06</v>
+        <v>245.518</v>
       </c>
       <c r="G72">
         <v>20.4</v>
@@ -7322,37 +7322,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M72">
-        <v>35.53440800000001</v>
+        <v>36.04204240000001</v>
       </c>
       <c r="N72">
-        <v>-6.454816163265313</v>
+        <v>-6.962450563265314</v>
       </c>
       <c r="O72">
-        <v>-1.549155879183675</v>
+        <v>-1.670988135183675</v>
       </c>
       <c r="P72">
-        <v>-4.905660284081638</v>
+        <v>-5.291462428081639</v>
       </c>
       <c r="Q72">
-        <v>-0.005660284081639766</v>
+        <v>-0.3914624280816401</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1908036616851395</v>
+        <v>0.1958037879501443</v>
       </c>
       <c r="T72">
-        <v>2.444970051405196</v>
+        <v>2.529279363522617</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1964040611234138</v>
+        <v>0.1936378067413939</v>
       </c>
       <c r="W72">
-        <v>0.1179678838270829</v>
+        <v>0.1183739699703634</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.818350254680891</v>
+        <v>0.8068241947558079</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1408286171844998</v>
+        <v>0.1825833260525342</v>
       </c>
       <c r="C73">
-        <v>-60.70617203293949</v>
+        <v>-114.3528040054457</v>
       </c>
       <c r="D73">
-        <v>164.4118279670605</v>
+        <v>114.2231959945543</v>
       </c>
       <c r="E73">
-        <v>157.518</v>
+        <v>160.976</v>
       </c>
       <c r="F73">
-        <v>245.518</v>
+        <v>248.976</v>
       </c>
       <c r="G73">
         <v>20.4</v>
@@ -7404,45 +7404,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M73">
-        <v>36.04204240000001</v>
+        <v>49.9943808</v>
       </c>
       <c r="N73">
-        <v>-6.962450563265314</v>
+        <v>-20.91478896326531</v>
       </c>
       <c r="O73">
-        <v>-1.670988135183675</v>
+        <v>-5.019549351183674</v>
       </c>
       <c r="P73">
-        <v>-5.291462428081639</v>
+        <v>-15.89523961208164</v>
       </c>
       <c r="Q73">
-        <v>-0.3914624280816401</v>
+        <v>-10.99523961208164</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1958037879501442</v>
+        <v>0.2078207406199152</v>
       </c>
       <c r="T73">
-        <v>2.529279363522616</v>
+        <v>2.731902449348833</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1936378067413939</v>
+        <v>0.1395977293675437</v>
       </c>
       <c r="W73">
-        <v>0.1183739699703634</v>
+        <v>0.1727687759429972</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8068241947558079</v>
+        <v>0.5816572056980991</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1825833260525342</v>
+        <v>0.1841333260525342</v>
       </c>
       <c r="C74">
-        <v>-114.3528040054457</v>
+        <v>-119.0906543411799</v>
       </c>
       <c r="D74">
-        <v>114.2231959945543</v>
+        <v>112.9433456588201</v>
       </c>
       <c r="E74">
-        <v>160.976</v>
+        <v>164.434</v>
       </c>
       <c r="F74">
-        <v>248.976</v>
+        <v>252.434</v>
       </c>
       <c r="G74">
         <v>20.4</v>
@@ -7486,37 +7486,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M74">
-        <v>49.9943808</v>
+        <v>50.6887472</v>
       </c>
       <c r="N74">
-        <v>-20.91478896326531</v>
+        <v>-21.60915536326531</v>
       </c>
       <c r="O74">
-        <v>-5.019549351183674</v>
+        <v>-5.186197287183674</v>
       </c>
       <c r="P74">
-        <v>-15.89523961208164</v>
+        <v>-16.42295807608163</v>
       </c>
       <c r="Q74">
-        <v>-10.99523961208164</v>
+        <v>-11.52295807608164</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2078207406199152</v>
+        <v>0.2138215087910232</v>
       </c>
       <c r="T74">
-        <v>2.731902449348833</v>
+        <v>2.833084021546938</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1395977293675437</v>
+        <v>0.1376854317049747</v>
       </c>
       <c r="W74">
-        <v>0.1727687759429972</v>
+        <v>0.1731527653136411</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5816572056980991</v>
+        <v>0.5736892987707278</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1841333260525342</v>
+        <v>0.1856833260525342</v>
       </c>
       <c r="C75">
-        <v>-119.0906543411799</v>
+        <v>-123.8001414963068</v>
       </c>
       <c r="D75">
-        <v>112.9433456588201</v>
+        <v>111.6918585036932</v>
       </c>
       <c r="E75">
-        <v>164.434</v>
+        <v>167.892</v>
       </c>
       <c r="F75">
-        <v>252.434</v>
+        <v>255.892</v>
       </c>
       <c r="G75">
         <v>20.4</v>
@@ -7568,37 +7568,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M75">
-        <v>50.6887472</v>
+        <v>51.3831136</v>
       </c>
       <c r="N75">
-        <v>-21.60915536326531</v>
+        <v>-22.30352176326531</v>
       </c>
       <c r="O75">
-        <v>-5.186197287183674</v>
+        <v>-5.352845223183674</v>
       </c>
       <c r="P75">
-        <v>-16.42295807608163</v>
+        <v>-16.95067654008163</v>
       </c>
       <c r="Q75">
-        <v>-11.52295807608164</v>
+        <v>-12.05067654008164</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2138215087910232</v>
+        <v>0.2202838745137548</v>
       </c>
       <c r="T75">
-        <v>2.833084021546938</v>
+        <v>2.942048791606435</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1376854317049747</v>
+        <v>0.1358248177630156</v>
       </c>
       <c r="W75">
-        <v>0.1731527653136411</v>
+        <v>0.1735263765931865</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5736892987707278</v>
+        <v>0.5659367406792315</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1856833260525342</v>
+        <v>0.1872333260525343</v>
       </c>
       <c r="C76">
-        <v>-123.8001414963068</v>
+        <v>-128.4821979864753</v>
       </c>
       <c r="D76">
-        <v>111.6918585036932</v>
+        <v>110.4678020135247</v>
       </c>
       <c r="E76">
-        <v>167.892</v>
+        <v>171.35</v>
       </c>
       <c r="F76">
-        <v>255.892</v>
+        <v>259.35</v>
       </c>
       <c r="G76">
         <v>20.4</v>
@@ -7650,37 +7650,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M76">
-        <v>51.3831136</v>
+        <v>52.07748000000001</v>
       </c>
       <c r="N76">
-        <v>-22.30352176326531</v>
+        <v>-22.99788816326532</v>
       </c>
       <c r="O76">
-        <v>-5.352845223183674</v>
+        <v>-5.519493159183676</v>
       </c>
       <c r="P76">
-        <v>-16.95067654008163</v>
+        <v>-17.47839500408164</v>
       </c>
       <c r="Q76">
-        <v>-12.05067654008164</v>
+        <v>-12.57839500408164</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2202838745137548</v>
+        <v>0.227263229494305</v>
       </c>
       <c r="T76">
-        <v>2.942048791606435</v>
+        <v>3.059730743270693</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1358248177630156</v>
+        <v>0.134013820192842</v>
       </c>
       <c r="W76">
-        <v>0.1735263765931865</v>
+        <v>0.1738900249052773</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5659367406792315</v>
+        <v>0.558390917470175</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1872333260525343</v>
+        <v>0.1887833260525343</v>
       </c>
       <c r="C77">
-        <v>-128.4821979864753</v>
+        <v>-133.1377158918712</v>
       </c>
       <c r="D77">
-        <v>110.4678020135247</v>
+        <v>109.2702841081288</v>
       </c>
       <c r="E77">
-        <v>171.35</v>
+        <v>174.808</v>
       </c>
       <c r="F77">
-        <v>259.35</v>
+        <v>262.808</v>
       </c>
       <c r="G77">
         <v>20.4</v>
@@ -7732,37 +7732,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M77">
-        <v>52.07748000000001</v>
+        <v>52.7718464</v>
       </c>
       <c r="N77">
-        <v>-22.99788816326532</v>
+        <v>-23.69225456326531</v>
       </c>
       <c r="O77">
-        <v>-5.519493159183676</v>
+        <v>-5.686141095183673</v>
       </c>
       <c r="P77">
-        <v>-17.47839500408164</v>
+        <v>-18.00611346808164</v>
       </c>
       <c r="Q77">
-        <v>-12.57839500408164</v>
+        <v>-13.10611346808164</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.227263229494305</v>
+        <v>0.2348241973899011</v>
       </c>
       <c r="T77">
-        <v>3.059730743270693</v>
+        <v>3.187219524240305</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.134013820192842</v>
+        <v>0.1322504804534625</v>
       </c>
       <c r="W77">
-        <v>0.1738900249052773</v>
+        <v>0.1742441035249447</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.558390917470175</v>
+        <v>0.5510436685560938</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1887833260525343</v>
+        <v>0.1903333260525343</v>
       </c>
       <c r="C78">
-        <v>-133.1377158918712</v>
+        <v>-137.7675490254008</v>
       </c>
       <c r="D78">
-        <v>109.2702841081288</v>
+        <v>108.0984509745992</v>
       </c>
       <c r="E78">
-        <v>174.808</v>
+        <v>178.266</v>
       </c>
       <c r="F78">
-        <v>262.808</v>
+        <v>266.266</v>
       </c>
       <c r="G78">
         <v>20.4</v>
@@ -7814,37 +7814,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M78">
-        <v>52.7718464</v>
+        <v>53.46621280000001</v>
       </c>
       <c r="N78">
-        <v>-23.69225456326531</v>
+        <v>-24.38662096326532</v>
       </c>
       <c r="O78">
-        <v>-5.686141095183673</v>
+        <v>-5.852789031183676</v>
       </c>
       <c r="P78">
-        <v>-18.00611346808164</v>
+        <v>-18.53383193208164</v>
       </c>
       <c r="Q78">
-        <v>-13.10611346808164</v>
+        <v>-13.63383193208164</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2348241973899011</v>
+        <v>0.2430426407546794</v>
       </c>
       <c r="T78">
-        <v>3.187219524240305</v>
+        <v>3.325794286163797</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1322504804534625</v>
+        <v>0.1305329417462747</v>
       </c>
       <c r="W78">
-        <v>0.1742441035249447</v>
+        <v>0.1745889852973481</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5510436685560938</v>
+        <v>0.5438872572761444</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1903333260525343</v>
+        <v>0.1918833260525343</v>
       </c>
       <c r="C79">
-        <v>-137.7675490254008</v>
+        <v>-142.3725149628438</v>
       </c>
       <c r="D79">
-        <v>108.0984509745992</v>
+        <v>106.9514850371563</v>
       </c>
       <c r="E79">
-        <v>178.266</v>
+        <v>181.724</v>
       </c>
       <c r="F79">
-        <v>266.266</v>
+        <v>269.724</v>
       </c>
       <c r="G79">
         <v>20.4</v>
@@ -7896,37 +7896,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M79">
-        <v>53.46621280000001</v>
+        <v>54.16057920000001</v>
       </c>
       <c r="N79">
-        <v>-24.38662096326532</v>
+        <v>-25.08098736326532</v>
       </c>
       <c r="O79">
-        <v>-5.852789031183676</v>
+        <v>-6.019436967183675</v>
       </c>
       <c r="P79">
-        <v>-18.53383193208164</v>
+        <v>-19.06155039608164</v>
       </c>
       <c r="Q79">
-        <v>-13.63383193208164</v>
+        <v>-14.16155039608164</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2430426407546794</v>
+        <v>0.2520082153344375</v>
       </c>
       <c r="T79">
-        <v>3.325794286163797</v>
+        <v>3.476966753716697</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1305329417462747</v>
+        <v>0.1288594424931173</v>
       </c>
       <c r="W79">
-        <v>0.1745889852973481</v>
+        <v>0.174925023947382</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5438872572761444</v>
+        <v>0.5369143437213222</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1918833260525343</v>
+        <v>0.1934333260525343</v>
       </c>
       <c r="C80">
-        <v>-142.3725149628438</v>
+        <v>-146.9533969451179</v>
       </c>
       <c r="D80">
-        <v>106.9514850371563</v>
+        <v>105.8286030548821</v>
       </c>
       <c r="E80">
-        <v>181.724</v>
+        <v>185.182</v>
       </c>
       <c r="F80">
-        <v>269.724</v>
+        <v>273.182</v>
       </c>
       <c r="G80">
         <v>20.4</v>
@@ -7978,37 +7978,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M80">
-        <v>54.16057920000001</v>
+        <v>54.85494560000001</v>
       </c>
       <c r="N80">
-        <v>-25.08098736326532</v>
+        <v>-25.77535376326531</v>
       </c>
       <c r="O80">
-        <v>-6.019436967183675</v>
+        <v>-6.186084903183676</v>
       </c>
       <c r="P80">
-        <v>-19.06155039608164</v>
+        <v>-19.58926886008164</v>
       </c>
       <c r="Q80">
-        <v>-14.16155039608164</v>
+        <v>-14.68926886008164</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2520082153344375</v>
+        <v>0.261827654159887</v>
       </c>
       <c r="T80">
-        <v>3.476966753716697</v>
+        <v>3.642536599131779</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1288594424931173</v>
+        <v>0.1272283103096601</v>
       </c>
       <c r="W80">
-        <v>0.174925023947382</v>
+        <v>0.1752525552898203</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5369143437213222</v>
+        <v>0.5301179596235839</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1934333260525343</v>
+        <v>0.1949833260525343</v>
       </c>
       <c r="C81">
-        <v>-146.9533969451179</v>
+        <v>-151.5109456619585</v>
       </c>
       <c r="D81">
-        <v>105.8286030548821</v>
+        <v>104.7290543380416</v>
       </c>
       <c r="E81">
-        <v>185.182</v>
+        <v>188.64</v>
       </c>
       <c r="F81">
-        <v>273.182</v>
+        <v>276.64</v>
       </c>
       <c r="G81">
         <v>20.4</v>
@@ -8060,37 +8060,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M81">
-        <v>54.85494560000001</v>
+        <v>55.54931200000001</v>
       </c>
       <c r="N81">
-        <v>-25.77535376326531</v>
+        <v>-26.46972016326531</v>
       </c>
       <c r="O81">
-        <v>-6.186084903183676</v>
+        <v>-6.352732839183675</v>
       </c>
       <c r="P81">
-        <v>-19.58926886008164</v>
+        <v>-20.11698732408164</v>
       </c>
       <c r="Q81">
-        <v>-14.68926886008164</v>
+        <v>-15.21698732408164</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.261827654159887</v>
+        <v>0.2726290368678813</v>
       </c>
       <c r="T81">
-        <v>3.642536599131779</v>
+        <v>3.824663429088368</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1272283103096601</v>
+        <v>0.1256379564307894</v>
       </c>
       <c r="W81">
-        <v>0.1752525552898203</v>
+        <v>0.1755718983486975</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5301179596235839</v>
+        <v>0.523491485128289</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1949833260525343</v>
+        <v>0.1965333260525343</v>
       </c>
       <c r="C82">
-        <v>-151.5109456619585</v>
+        <v>-156.045880925547</v>
       </c>
       <c r="D82">
-        <v>104.7290543380416</v>
+        <v>103.6521190744531</v>
       </c>
       <c r="E82">
-        <v>188.64</v>
+        <v>192.098</v>
       </c>
       <c r="F82">
-        <v>276.64</v>
+        <v>280.098</v>
       </c>
       <c r="G82">
         <v>20.4</v>
@@ -8142,37 +8142,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M82">
-        <v>55.54931200000001</v>
+        <v>56.24367840000001</v>
       </c>
       <c r="N82">
-        <v>-26.46972016326531</v>
+        <v>-27.16408656326531</v>
       </c>
       <c r="O82">
-        <v>-6.352732839183675</v>
+        <v>-6.519380775183675</v>
       </c>
       <c r="P82">
-        <v>-20.11698732408164</v>
+        <v>-20.64470578808164</v>
       </c>
       <c r="Q82">
-        <v>-15.21698732408164</v>
+        <v>-15.74470578808164</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2726290368678813</v>
+        <v>0.2845674072293488</v>
       </c>
       <c r="T82">
-        <v>3.824663429088368</v>
+        <v>4.025961504303544</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1256379564307894</v>
+        <v>0.1240868705489278</v>
       </c>
       <c r="W82">
-        <v>0.1755718983486975</v>
+        <v>0.1758833563937753</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.523491485128289</v>
+        <v>0.5170286272871991</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1965333260525343</v>
+        <v>0.1980833260525343</v>
       </c>
       <c r="C83">
-        <v>-156.045880925547</v>
+        <v>-160.5588932419314</v>
       </c>
       <c r="D83">
-        <v>103.6521190744531</v>
+        <v>102.5971067580687</v>
       </c>
       <c r="E83">
-        <v>192.098</v>
+        <v>195.556</v>
       </c>
       <c r="F83">
-        <v>280.098</v>
+        <v>283.556</v>
       </c>
       <c r="G83">
         <v>20.4</v>
@@ -8224,37 +8224,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M83">
-        <v>56.24367840000001</v>
+        <v>56.93804480000001</v>
       </c>
       <c r="N83">
-        <v>-27.16408656326531</v>
+        <v>-27.85845296326531</v>
       </c>
       <c r="O83">
-        <v>-6.519380775183675</v>
+        <v>-6.686028711183675</v>
       </c>
       <c r="P83">
-        <v>-20.64470578808164</v>
+        <v>-21.17242425208164</v>
       </c>
       <c r="Q83">
-        <v>-15.74470578808164</v>
+        <v>-16.27242425208164</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2845674072293488</v>
+        <v>0.2978322631865348</v>
       </c>
       <c r="T83">
-        <v>4.025961504303544</v>
+        <v>4.249626032320408</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1240868705489278</v>
+        <v>0.1225736160300384</v>
       </c>
       <c r="W83">
-        <v>0.1758833563937753</v>
+        <v>0.1761872179011683</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5170286272871991</v>
+        <v>0.51072340012516</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1980833260525343</v>
+        <v>0.1996333260525343</v>
       </c>
       <c r="C84">
-        <v>-160.5588932419314</v>
+        <v>-165.0506452874452</v>
       </c>
       <c r="D84">
-        <v>102.5971067580687</v>
+        <v>101.5633547125548</v>
       </c>
       <c r="E84">
-        <v>195.556</v>
+        <v>199.014</v>
       </c>
       <c r="F84">
-        <v>283.556</v>
+        <v>287.014</v>
       </c>
       <c r="G84">
         <v>20.4</v>
@@ -8306,37 +8306,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M84">
-        <v>56.93804480000001</v>
+        <v>57.63241120000001</v>
       </c>
       <c r="N84">
-        <v>-27.85845296326531</v>
+        <v>-28.55281936326531</v>
       </c>
       <c r="O84">
-        <v>-6.686028711183675</v>
+        <v>-6.852676647183675</v>
       </c>
       <c r="P84">
-        <v>-21.17242425208164</v>
+        <v>-21.70014271608164</v>
       </c>
       <c r="Q84">
-        <v>-16.27242425208164</v>
+        <v>-16.80014271608164</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2978322631865348</v>
+        <v>0.3126576904328016</v>
       </c>
       <c r="T84">
-        <v>4.249626032320408</v>
+        <v>4.499604034221609</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1225736160300384</v>
+        <v>0.1210968254754596</v>
       </c>
       <c r="W84">
-        <v>0.1761872179011683</v>
+        <v>0.1764837574445277</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.51072340012516</v>
+        <v>0.5045701061477486</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1996333260525343</v>
+        <v>0.2313357586039715</v>
       </c>
       <c r="C85">
-        <v>-165.0506452874452</v>
+        <v>-185.8627414826977</v>
       </c>
       <c r="D85">
-        <v>101.5633547125548</v>
+        <v>84.2092585173023</v>
       </c>
       <c r="E85">
-        <v>199.014</v>
+        <v>202.472</v>
       </c>
       <c r="F85">
-        <v>287.014</v>
+        <v>290.472</v>
       </c>
       <c r="G85">
         <v>20.4</v>
@@ -8388,45 +8388,45 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M85">
-        <v>57.63241120000001</v>
+        <v>68.49329760000001</v>
       </c>
       <c r="N85">
-        <v>-28.55281936326531</v>
+        <v>-39.41370576326531</v>
       </c>
       <c r="O85">
-        <v>-6.852676647183675</v>
+        <v>-9.459289383183675</v>
       </c>
       <c r="P85">
-        <v>-21.70014271608164</v>
+        <v>-29.95441638008164</v>
       </c>
       <c r="Q85">
-        <v>-16.80014271608164</v>
+        <v>-25.05441638008164</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3126576904328016</v>
+        <v>0.3340389995313346</v>
       </c>
       <c r="T85">
-        <v>4.499604034221609</v>
+        <v>4.860123622473553</v>
       </c>
       <c r="U85">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1210968254754596</v>
+        <v>0.1018946712359243</v>
       </c>
       <c r="W85">
-        <v>0.1764837574445277</v>
+        <v>0.211773236522569</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.5045701061477486</v>
+        <v>0.4245611301496848</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2313357586039715</v>
+        <v>0.2332357586039715</v>
       </c>
       <c r="C86">
-        <v>-185.8627414826976</v>
+        <v>-190.1743544345407</v>
       </c>
       <c r="D86">
-        <v>84.20925851730235</v>
+        <v>83.35564556545931</v>
       </c>
       <c r="E86">
-        <v>202.472</v>
+        <v>205.93</v>
       </c>
       <c r="F86">
-        <v>290.472</v>
+        <v>293.93</v>
       </c>
       <c r="G86">
         <v>20.4</v>
@@ -8470,37 +8470,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M86">
-        <v>68.49329759999999</v>
+        <v>69.308694</v>
       </c>
       <c r="N86">
-        <v>-39.4137057632653</v>
+        <v>-40.22910216326531</v>
       </c>
       <c r="O86">
-        <v>-9.459289383183672</v>
+        <v>-9.654984519183675</v>
       </c>
       <c r="P86">
-        <v>-29.95441638008162</v>
+        <v>-30.57411764408164</v>
       </c>
       <c r="Q86">
-        <v>-25.05441638008163</v>
+        <v>-25.67411764408164</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3340389995313344</v>
+        <v>0.3532549328334234</v>
       </c>
       <c r="T86">
-        <v>4.86012362247355</v>
+        <v>5.184131863971787</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1018946712359244</v>
+        <v>0.1006959103978547</v>
       </c>
       <c r="W86">
-        <v>0.211773236522569</v>
+        <v>0.2120559043281859</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4245611301496849</v>
+        <v>0.4195662933243943</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2332357586039715</v>
+        <v>0.2351357586039715</v>
       </c>
       <c r="C87">
-        <v>-190.1743544345407</v>
+        <v>-194.4688352332135</v>
       </c>
       <c r="D87">
-        <v>83.35564556545931</v>
+        <v>82.51916476678649</v>
       </c>
       <c r="E87">
-        <v>205.93</v>
+        <v>209.388</v>
       </c>
       <c r="F87">
-        <v>293.93</v>
+        <v>297.388</v>
       </c>
       <c r="G87">
         <v>20.4</v>
@@ -8552,37 +8552,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M87">
-        <v>69.308694</v>
+        <v>70.1240904</v>
       </c>
       <c r="N87">
-        <v>-40.22910216326531</v>
+        <v>-41.04449856326531</v>
       </c>
       <c r="O87">
-        <v>-9.654984519183675</v>
+        <v>-9.850679655183674</v>
       </c>
       <c r="P87">
-        <v>-30.57411764408164</v>
+        <v>-31.19381890808163</v>
       </c>
       <c r="Q87">
-        <v>-25.67411764408164</v>
+        <v>-26.29381890808163</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3532549328334234</v>
+        <v>0.3752159994643822</v>
       </c>
       <c r="T87">
-        <v>5.184131863971787</v>
+        <v>5.554426997112629</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1006959103978547</v>
+        <v>0.09952502771880983</v>
       </c>
       <c r="W87">
-        <v>0.2120559043281859</v>
+        <v>0.2123319984639047</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4195662933243943</v>
+        <v>0.414687615495041</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2351357586039715</v>
+        <v>0.2370357586039715</v>
       </c>
       <c r="C88">
-        <v>-194.4688352332135</v>
+        <v>-198.7466945220905</v>
       </c>
       <c r="D88">
-        <v>82.51916476678649</v>
+        <v>81.69930547790956</v>
       </c>
       <c r="E88">
-        <v>209.388</v>
+        <v>212.846</v>
       </c>
       <c r="F88">
-        <v>297.388</v>
+        <v>300.846</v>
       </c>
       <c r="G88">
         <v>20.4</v>
@@ -8634,37 +8634,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M88">
-        <v>70.1240904</v>
+        <v>70.9394868</v>
       </c>
       <c r="N88">
-        <v>-41.04449856326531</v>
+        <v>-41.8598949632653</v>
       </c>
       <c r="O88">
-        <v>-9.850679655183674</v>
+        <v>-10.04637479118367</v>
       </c>
       <c r="P88">
-        <v>-31.19381890808163</v>
+        <v>-31.81352017208163</v>
       </c>
       <c r="Q88">
-        <v>-26.29381890808163</v>
+        <v>-26.91352017208163</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3752159994643822</v>
+        <v>0.4005556917308731</v>
       </c>
       <c r="T88">
-        <v>5.554426997112629</v>
+        <v>5.981690612275139</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09952502771880983</v>
+        <v>0.09838106188296143</v>
       </c>
       <c r="W88">
-        <v>0.2123319984639047</v>
+        <v>0.2126017456079977</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.414687615495041</v>
+        <v>0.409921091179006</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2370357586039715</v>
+        <v>0.2389357586039715</v>
       </c>
       <c r="C89">
-        <v>-198.7466945220905</v>
+        <v>-203.0084228504439</v>
       </c>
       <c r="D89">
-        <v>81.69930547790956</v>
+        <v>80.89557714955616</v>
       </c>
       <c r="E89">
-        <v>212.846</v>
+        <v>216.304</v>
       </c>
       <c r="F89">
-        <v>300.846</v>
+        <v>304.304</v>
       </c>
       <c r="G89">
         <v>20.4</v>
@@ -8716,37 +8716,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M89">
-        <v>70.9394868</v>
+        <v>71.75488320000001</v>
       </c>
       <c r="N89">
-        <v>-41.8598949632653</v>
+        <v>-42.67529136326532</v>
       </c>
       <c r="O89">
-        <v>-10.04637479118367</v>
+        <v>-10.24206992718368</v>
       </c>
       <c r="P89">
-        <v>-31.81352017208163</v>
+        <v>-32.43322143608164</v>
       </c>
       <c r="Q89">
-        <v>-26.91352017208163</v>
+        <v>-27.53322143608164</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4005556917308731</v>
+        <v>0.4301186660417793</v>
       </c>
       <c r="T89">
-        <v>5.981690612275139</v>
+        <v>6.480164829964735</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09838106188296143</v>
+        <v>0.09726309527065505</v>
       </c>
       <c r="W89">
-        <v>0.2126017456079977</v>
+        <v>0.2128653621351796</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.409921091179006</v>
+        <v>0.4052628969610627</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2389357586039715</v>
+        <v>0.2408357586039715</v>
       </c>
       <c r="C90">
-        <v>-203.0084228504439</v>
+        <v>-207.2544916522077</v>
       </c>
       <c r="D90">
-        <v>80.89557714955616</v>
+        <v>80.10750834779225</v>
       </c>
       <c r="E90">
-        <v>216.304</v>
+        <v>219.762</v>
       </c>
       <c r="F90">
-        <v>304.304</v>
+        <v>307.762</v>
       </c>
       <c r="G90">
         <v>20.4</v>
@@ -8798,37 +8798,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M90">
-        <v>71.75488320000001</v>
+        <v>72.57027960000001</v>
       </c>
       <c r="N90">
-        <v>-42.67529136326532</v>
+        <v>-43.49068776326531</v>
       </c>
       <c r="O90">
-        <v>-10.24206992718368</v>
+        <v>-10.43776506318367</v>
       </c>
       <c r="P90">
-        <v>-32.43322143608164</v>
+        <v>-33.05292270008164</v>
       </c>
       <c r="Q90">
-        <v>-27.53322143608164</v>
+        <v>-28.15292270008164</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4301186660417793</v>
+        <v>0.465056726591032</v>
       </c>
       <c r="T90">
-        <v>6.480164829964735</v>
+        <v>7.069270723597893</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09726309527065505</v>
+        <v>0.09617025150356903</v>
       </c>
       <c r="W90">
-        <v>0.2128653621351796</v>
+        <v>0.2131230546954584</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4052628969610627</v>
+        <v>0.400709381264871</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2408357586039715</v>
+        <v>0.2427357586039715</v>
       </c>
       <c r="C91">
-        <v>-207.2544916522077</v>
+        <v>-211.4853541680848</v>
       </c>
       <c r="D91">
-        <v>80.10750834779225</v>
+        <v>79.33464583191522</v>
       </c>
       <c r="E91">
-        <v>219.762</v>
+        <v>223.22</v>
       </c>
       <c r="F91">
-        <v>307.762</v>
+        <v>311.22</v>
       </c>
       <c r="G91">
         <v>20.4</v>
@@ -8880,37 +8880,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M91">
-        <v>72.57027960000001</v>
+        <v>73.385676</v>
       </c>
       <c r="N91">
-        <v>-43.49068776326531</v>
+        <v>-44.30608416326531</v>
       </c>
       <c r="O91">
-        <v>-10.43776506318367</v>
+        <v>-10.63346019918367</v>
       </c>
       <c r="P91">
-        <v>-33.05292270008164</v>
+        <v>-33.67262396408164</v>
       </c>
       <c r="Q91">
-        <v>-28.15292270008164</v>
+        <v>-28.77262396408164</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.465056726591032</v>
+        <v>0.5069823992501352</v>
       </c>
       <c r="T91">
-        <v>7.069270723597893</v>
+        <v>7.776197795957684</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09617025150356903</v>
+        <v>0.09510169315352938</v>
       </c>
       <c r="W91">
-        <v>0.2131230546954584</v>
+        <v>0.2133750207543978</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.400709381264871</v>
+        <v>0.3962570548063724</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2427357586039715</v>
+        <v>0.2446357586039715</v>
       </c>
       <c r="C92">
-        <v>-211.4853541680848</v>
+        <v>-215.7014463147839</v>
       </c>
       <c r="D92">
-        <v>79.33464583191522</v>
+        <v>78.57655368521611</v>
       </c>
       <c r="E92">
-        <v>223.22</v>
+        <v>226.678</v>
       </c>
       <c r="F92">
-        <v>311.22</v>
+        <v>314.678</v>
       </c>
       <c r="G92">
         <v>20.4</v>
@@ -8962,37 +8962,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M92">
-        <v>73.385676</v>
+        <v>74.2010724</v>
       </c>
       <c r="N92">
-        <v>-44.30608416326531</v>
+        <v>-45.12148056326531</v>
       </c>
       <c r="O92">
-        <v>-10.63346019918367</v>
+        <v>-10.82915533518367</v>
       </c>
       <c r="P92">
-        <v>-33.67262396408164</v>
+        <v>-34.29232522808164</v>
       </c>
       <c r="Q92">
-        <v>-28.77262396408164</v>
+        <v>-29.39232522808164</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5069823992501352</v>
+        <v>0.5582248880557058</v>
       </c>
       <c r="T92">
-        <v>7.776197795957684</v>
+        <v>8.640219773286315</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09510169315352938</v>
+        <v>0.0940566196023917</v>
       </c>
       <c r="W92">
-        <v>0.2133750207543978</v>
+        <v>0.213621449097756</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3962570548063724</v>
+        <v>0.3919025816766321</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2446357586039715</v>
+        <v>0.2465357586039715</v>
       </c>
       <c r="C93">
-        <v>-215.7014463147839</v>
+        <v>-219.9031875048947</v>
       </c>
       <c r="D93">
-        <v>78.57655368521611</v>
+        <v>77.83281249510532</v>
       </c>
       <c r="E93">
-        <v>226.678</v>
+        <v>230.136</v>
       </c>
       <c r="F93">
-        <v>314.678</v>
+        <v>318.136</v>
       </c>
       <c r="G93">
         <v>20.4</v>
@@ -9044,37 +9044,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M93">
-        <v>74.2010724</v>
+        <v>75.01646880000001</v>
       </c>
       <c r="N93">
-        <v>-45.12148056326531</v>
+        <v>-45.93687696326532</v>
       </c>
       <c r="O93">
-        <v>-10.82915533518367</v>
+        <v>-11.02485047118368</v>
       </c>
       <c r="P93">
-        <v>-34.29232522808164</v>
+        <v>-34.91202649208164</v>
       </c>
       <c r="Q93">
-        <v>-29.39232522808164</v>
+        <v>-30.01202649208165</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5582248880557058</v>
+        <v>0.6222779990626692</v>
       </c>
       <c r="T93">
-        <v>8.640219773286315</v>
+        <v>9.720247244947107</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0940566196023917</v>
+        <v>0.09303426504149613</v>
       </c>
       <c r="W93">
-        <v>0.213621449097756</v>
+        <v>0.2138625203032152</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3919025816766321</v>
+        <v>0.3876427710062339</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2465357586039715</v>
+        <v>0.2484357586039715</v>
       </c>
       <c r="C94">
-        <v>-219.9031875048947</v>
+        <v>-224.0909814206356</v>
       </c>
       <c r="D94">
-        <v>77.83281249510532</v>
+        <v>77.1030185793645</v>
       </c>
       <c r="E94">
-        <v>230.136</v>
+        <v>233.5940000000001</v>
       </c>
       <c r="F94">
-        <v>318.136</v>
+        <v>321.5940000000001</v>
       </c>
       <c r="G94">
         <v>20.4</v>
@@ -9126,37 +9126,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M94">
-        <v>75.01646880000001</v>
+        <v>75.83186520000001</v>
       </c>
       <c r="N94">
-        <v>-45.93687696326532</v>
+        <v>-46.75227336326532</v>
       </c>
       <c r="O94">
-        <v>-11.02485047118368</v>
+        <v>-11.22054560718368</v>
       </c>
       <c r="P94">
-        <v>-34.91202649208164</v>
+        <v>-35.53172775608164</v>
       </c>
       <c r="Q94">
-        <v>-30.01202649208165</v>
+        <v>-30.63172775608164</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6222779990626692</v>
+        <v>0.7046319989287649</v>
       </c>
       <c r="T94">
-        <v>9.720247244947107</v>
+        <v>11.10885399422527</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09303426504149613</v>
+        <v>0.09203389660018972</v>
       </c>
       <c r="W94">
-        <v>0.2138625203032152</v>
+        <v>0.2140984071816753</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3876427710062339</v>
+        <v>0.3834745691674571</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2484357586039715</v>
+        <v>0.2503357586039715</v>
       </c>
       <c r="C95">
-        <v>-224.0909814206356</v>
+        <v>-228.2652167444766</v>
       </c>
       <c r="D95">
-        <v>77.1030185793645</v>
+        <v>76.38678325552343</v>
       </c>
       <c r="E95">
-        <v>233.5940000000001</v>
+        <v>237.052</v>
       </c>
       <c r="F95">
-        <v>321.5940000000001</v>
+        <v>325.052</v>
       </c>
       <c r="G95">
         <v>20.4</v>
@@ -9208,37 +9208,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M95">
-        <v>75.83186520000001</v>
+        <v>76.64726160000001</v>
       </c>
       <c r="N95">
-        <v>-46.75227336326532</v>
+        <v>-47.56766976326531</v>
       </c>
       <c r="O95">
-        <v>-11.22054560718368</v>
+        <v>-11.41624074318367</v>
       </c>
       <c r="P95">
-        <v>-35.53172775608164</v>
+        <v>-36.15142902008164</v>
       </c>
       <c r="Q95">
-        <v>-30.63172775608164</v>
+        <v>-31.25142902008164</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7046319989287649</v>
+        <v>0.8144373320835592</v>
       </c>
       <c r="T95">
-        <v>11.10885399422527</v>
+        <v>12.96032965992948</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09203389660018972</v>
+        <v>0.09105481259380473</v>
       </c>
       <c r="W95">
-        <v>0.2140984071816753</v>
+        <v>0.2143292751903808</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3834745691674571</v>
+        <v>0.3793950524741864</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2503357586039715</v>
+        <v>0.2522357586039715</v>
       </c>
       <c r="C96">
-        <v>-228.2652167444766</v>
+        <v>-232.4262678494159</v>
       </c>
       <c r="D96">
-        <v>76.38678325552343</v>
+        <v>75.68373215058419</v>
       </c>
       <c r="E96">
-        <v>237.052</v>
+        <v>240.51</v>
       </c>
       <c r="F96">
-        <v>325.052</v>
+        <v>328.51</v>
       </c>
       <c r="G96">
         <v>20.4</v>
@@ -9290,37 +9290,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M96">
-        <v>76.64726160000001</v>
+        <v>77.46265800000002</v>
       </c>
       <c r="N96">
-        <v>-47.56766976326531</v>
+        <v>-48.38306616326533</v>
       </c>
       <c r="O96">
-        <v>-11.41624074318367</v>
+        <v>-11.61193587918368</v>
       </c>
       <c r="P96">
-        <v>-36.15142902008164</v>
+        <v>-36.77113028408165</v>
       </c>
       <c r="Q96">
-        <v>-31.25142902008164</v>
+        <v>-31.87113028408165</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8144373320835592</v>
+        <v>0.9681647985002716</v>
       </c>
       <c r="T96">
-        <v>12.96032965992948</v>
+        <v>15.55239559191538</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09105481259380473</v>
+        <v>0.09009634088229099</v>
       </c>
       <c r="W96">
-        <v>0.2143292751903808</v>
+        <v>0.2145552828199558</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3793950524741864</v>
+        <v>0.375401420342879</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2522357586039715</v>
+        <v>0.2541357586039715</v>
       </c>
       <c r="C97">
-        <v>-232.4262678494159</v>
+        <v>-236.5744954514832</v>
       </c>
       <c r="D97">
-        <v>75.68373215058419</v>
+        <v>74.99350454851681</v>
       </c>
       <c r="E97">
-        <v>240.51</v>
+        <v>243.968</v>
       </c>
       <c r="F97">
-        <v>328.51</v>
+        <v>331.968</v>
       </c>
       <c r="G97">
         <v>20.4</v>
@@ -9372,37 +9372,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M97">
-        <v>77.46265800000002</v>
+        <v>78.2780544</v>
       </c>
       <c r="N97">
-        <v>-48.38306616326533</v>
+        <v>-49.19846256326531</v>
       </c>
       <c r="O97">
-        <v>-11.61193587918368</v>
+        <v>-11.80763101518367</v>
       </c>
       <c r="P97">
-        <v>-36.77113028408165</v>
+        <v>-37.39083154808164</v>
       </c>
       <c r="Q97">
-        <v>-31.87113028408165</v>
+        <v>-32.49083154808164</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9681647985002716</v>
+        <v>1.19875599812534</v>
       </c>
       <c r="T97">
-        <v>15.55239559191538</v>
+        <v>19.44049448989424</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09009634088229099</v>
+        <v>0.0891578373314338</v>
       </c>
       <c r="W97">
-        <v>0.2145552828199558</v>
+        <v>0.2147765819572479</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.375401420342879</v>
+        <v>0.3714909888809742</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2541357586039715</v>
+        <v>0.2560357586039715</v>
       </c>
       <c r="C98">
-        <v>-236.5744954514832</v>
+        <v>-240.7102472268631</v>
       </c>
       <c r="D98">
-        <v>74.99350454851681</v>
+        <v>74.31575277313691</v>
       </c>
       <c r="E98">
-        <v>243.968</v>
+        <v>247.426</v>
       </c>
       <c r="F98">
-        <v>331.968</v>
+        <v>335.426</v>
       </c>
       <c r="G98">
         <v>20.4</v>
@@ -9454,37 +9454,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M98">
-        <v>78.2780544</v>
+        <v>79.0934508</v>
       </c>
       <c r="N98">
-        <v>-49.19846256326531</v>
+        <v>-50.01385896326531</v>
       </c>
       <c r="O98">
-        <v>-11.80763101518367</v>
+        <v>-12.00332615118367</v>
       </c>
       <c r="P98">
-        <v>-37.39083154808164</v>
+        <v>-38.01053281208164</v>
       </c>
       <c r="Q98">
-        <v>-32.49083154808164</v>
+        <v>-33.11053281208164</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.198755998125337</v>
+        <v>1.583074664167116</v>
       </c>
       <c r="T98">
-        <v>19.44049448989419</v>
+        <v>25.92065931985891</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0891578373314338</v>
+        <v>0.08823868436925407</v>
       </c>
       <c r="W98">
-        <v>0.2147765819572479</v>
+        <v>0.2149933182257299</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3714909888809742</v>
+        <v>0.367661184871892</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2560357586039715</v>
+        <v>0.2579357586039715</v>
       </c>
       <c r="C99">
-        <v>-240.7102472268631</v>
+        <v>-244.833858395853</v>
       </c>
       <c r="D99">
-        <v>74.31575277313691</v>
+        <v>73.65014160414697</v>
       </c>
       <c r="E99">
-        <v>247.426</v>
+        <v>250.884</v>
       </c>
       <c r="F99">
-        <v>335.426</v>
+        <v>338.884</v>
       </c>
       <c r="G99">
         <v>20.4</v>
@@ -9536,37 +9536,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M99">
-        <v>79.0934508</v>
+        <v>79.90884720000001</v>
       </c>
       <c r="N99">
-        <v>-50.01385896326531</v>
+        <v>-50.82925536326532</v>
       </c>
       <c r="O99">
-        <v>-12.00332615118367</v>
+        <v>-12.19902128718368</v>
       </c>
       <c r="P99">
-        <v>-38.01053281208164</v>
+        <v>-38.63023407608164</v>
       </c>
       <c r="Q99">
-        <v>-33.11053281208164</v>
+        <v>-33.73023407608164</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.583074664167116</v>
+        <v>2.351711996250674</v>
       </c>
       <c r="T99">
-        <v>25.92065931985891</v>
+        <v>38.88098897978838</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08823868436925407</v>
+        <v>0.08733828963079228</v>
       </c>
       <c r="W99">
-        <v>0.2149933182257299</v>
+        <v>0.2152056313050592</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.367661184871892</v>
+        <v>0.3639095401283012</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2579357586039715</v>
+        <v>0.2598357586039715</v>
       </c>
       <c r="C100">
-        <v>-244.833858395853</v>
+        <v>-248.9456522757196</v>
       </c>
       <c r="D100">
-        <v>73.65014160414697</v>
+        <v>72.99634772428037</v>
       </c>
       <c r="E100">
-        <v>250.884</v>
+        <v>254.342</v>
       </c>
       <c r="F100">
-        <v>338.884</v>
+        <v>342.342</v>
       </c>
       <c r="G100">
         <v>20.4</v>
@@ -9618,37 +9618,37 @@
         <v>29.07959183673469</v>
       </c>
       <c r="M100">
-        <v>79.90884720000001</v>
+        <v>80.72424359999999</v>
       </c>
       <c r="N100">
-        <v>-50.82925536326532</v>
+        <v>-51.6446517632653</v>
       </c>
       <c r="O100">
-        <v>-12.19902128718368</v>
+        <v>-12.39471642318367</v>
       </c>
       <c r="P100">
-        <v>-38.63023407608164</v>
+        <v>-39.24993534008163</v>
       </c>
       <c r="Q100">
-        <v>-33.73023407608164</v>
+        <v>-34.34993534008163</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.351711996250674</v>
+        <v>4.657623992501347</v>
       </c>
       <c r="T100">
-        <v>38.88098897978838</v>
+        <v>77.76197795957674</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08733828963079228</v>
+        <v>0.08645608468502672</v>
       </c>
       <c r="W100">
-        <v>0.2152056313050592</v>
+        <v>0.2154136552312707</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3639095401283012</v>
+        <v>0.3602336861876113</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2598357586039715</v>
-      </c>
-      <c r="C101">
-        <v>-248.9456522757196</v>
-      </c>
-      <c r="D101">
-        <v>72.99634772428037</v>
-      </c>
-      <c r="E101">
-        <v>254.342</v>
-      </c>
-      <c r="F101">
-        <v>342.342</v>
-      </c>
-      <c r="G101">
-        <v>20.4</v>
-      </c>
-      <c r="H101">
-        <v>257.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33.97959183673469</v>
-      </c>
-      <c r="K101">
-        <v>4.899999999999999</v>
-      </c>
-      <c r="L101">
-        <v>29.07959183673469</v>
-      </c>
-      <c r="M101">
-        <v>80.72424359999999</v>
-      </c>
-      <c r="N101">
-        <v>-51.6446517632653</v>
-      </c>
-      <c r="O101">
-        <v>-12.39471642318367</v>
-      </c>
-      <c r="P101">
-        <v>-39.24993534008163</v>
-      </c>
-      <c r="Q101">
-        <v>-34.34993534008163</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.657623992501347</v>
-      </c>
-      <c r="T101">
-        <v>77.76197795957674</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08645608468502672</v>
-      </c>
-      <c r="W101">
-        <v>0.2154136552312707</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3602336861876113</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
